--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -952,7 +952,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Compiled from the Yartseva–Pew–Berezin asymmetry framework  ·  Filtered to Nano / Micro / Small-Cap buckets  ·  As of 20 June 2026</t>
+          <t>Compiled from the asymmetry framework (Yartseva-aligned upside, Graham downside floor)  ·  Nano / Micro / Small-Cap buckets  ·  As of 24 June 2026</t>
         </is>
       </c>
     </row>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -970,7 +970,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,612-equity global universe, restricted to the 17,810 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,612-equity global universe, restricted to the 17,815 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>17,810</t>
+          <t>17,815</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -970,7 +970,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,612-equity global universe, restricted to the 17,815 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,558-equity global universe, restricted to the 17,770 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>25,612</t>
+          <t>25,558</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>17,815</t>
+          <t>17,770</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="C5" s="52" t="n">
-        <v>25612</v>
+        <v>25558</v>
       </c>
       <c r="D5" s="37" t="n">
         <v>131</v>
@@ -9972,10 +9972,10 @@
         <v>132</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>25138</v>
+        <v>25084</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>1.850694986724972</v>
+        <v>1.854605211675405</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -143,42 +143,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -1,126 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Global_Top_100" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="R_NorthAmerica" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="R_LatinAmerica" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="R_EU_Core" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="R_EU_Nordics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="R_EU_Periphery" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="R_EU_CEE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="R_Asia_Dev" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="R_Asia_Em" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="R_MEA" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="01_088910_KQ" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="02_AWC_SI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="03_2230_HK" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="04_0057_HK" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="05_003650_KS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="06_ZENIFIB_BO" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="07_SHRIDINE_BO" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="08_TPP_BK" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="09_0882_HK" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="10_ALGEV_PA" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="11_6155_T" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="12_0100_KL" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="13_IRC_BK" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="14_JAMESWARREN_BO" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="15_4301_T" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="16_2348_HK" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="17_S23_SI" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="18_4629_T" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="19_1798_T" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="20_FPIP_ST" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="21_6907_T" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="22_014570_KQ" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="23_NPK_BK" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="24_HTMEDIA_BO" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="25_052330_KQ" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="26_120240_KQ" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="27_6986_T" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="28_035610_KQ" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="29_0114_HK" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="30_BENGALT_BO" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="31_SIAM_BK" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="32_036190_KQ" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="33_PRIMEPRO_BO" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="34_7722_T" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="35_METCO_BK" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="36_0420_HK" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="37_2033_HK" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="38_031510_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="39_1795_T" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="40_047820_KQ" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="41_0212_HK" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="42_PBMPOLY_BO" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="43_054800_KQ" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="44_015230_KS" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="45_0538_HK" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="46_0887_HK" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="47_7219_T" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="48_053980_KQ" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="49_TMC-R_BK" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="50_0018_HK" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="51_7871_T" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="52_219420_KQ" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="53_CILSEC_BO" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="54_7614_T" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="55_1758_T" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="56_200570_SZ" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="57_3828_HK" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="58_HGS_BO" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="59_HGS_NS" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="60_4625_T" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="61_NPK-R_BK" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="62_HMVL_BO" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="63_HMVL_NS" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="64_3908_T" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="65_MANALIPETC_NS" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="66_016090_KS" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="67_7877_T" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet name="68_214320_KS" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet name="69_7851_T" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet name="70_4170_T" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet name="71_0865_HK" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet name="72_1118_HK" sheetId="84" state="visible" r:id="rId84"/>
-    <sheet name="73_HCO_PA" sheetId="85" state="visible" r:id="rId85"/>
-    <sheet name="74_9625_T" sheetId="86" state="visible" r:id="rId86"/>
-    <sheet name="75_BAI_SI" sheetId="87" state="visible" r:id="rId87"/>
-    <sheet name="76_3054_T" sheetId="88" state="visible" r:id="rId88"/>
-    <sheet name="77_SFG1T_TL" sheetId="89" state="visible" r:id="rId89"/>
-    <sheet name="78_051160_KQ" sheetId="90" state="visible" r:id="rId90"/>
-    <sheet name="79_0927_HK" sheetId="91" state="visible" r:id="rId91"/>
-    <sheet name="80_BEC_BK" sheetId="92" state="visible" r:id="rId92"/>
-    <sheet name="81_8119_T" sheetId="93" state="visible" r:id="rId93"/>
-    <sheet name="82_PURPLE_BO" sheetId="94" state="visible" r:id="rId94"/>
-    <sheet name="83_133750_KQ" sheetId="95" state="visible" r:id="rId95"/>
-    <sheet name="84_043610_KQ" sheetId="96" state="visible" r:id="rId96"/>
-    <sheet name="85_7057_T" sheetId="97" state="visible" r:id="rId97"/>
-    <sheet name="86_SKAKO_CO" sheetId="98" state="visible" r:id="rId98"/>
-    <sheet name="87_POONADAL_BO" sheetId="99" state="visible" r:id="rId99"/>
-    <sheet name="88_002758_SZ" sheetId="100" state="visible" r:id="rId100"/>
-    <sheet name="89_000850_KS" sheetId="101" state="visible" r:id="rId101"/>
-    <sheet name="90_0236_HK" sheetId="102" state="visible" r:id="rId102"/>
-    <sheet name="91_5MZ_SI" sheetId="103" state="visible" r:id="rId103"/>
-    <sheet name="92_0149_KL" sheetId="104" state="visible" r:id="rId104"/>
-    <sheet name="93_3954_T" sheetId="105" state="visible" r:id="rId105"/>
-    <sheet name="94_5951_T" sheetId="106" state="visible" r:id="rId106"/>
-    <sheet name="95_0411_HK" sheetId="107" state="visible" r:id="rId107"/>
-    <sheet name="96_7446_T" sheetId="108" state="visible" r:id="rId108"/>
-    <sheet name="97_9918_HK" sheetId="109" state="visible" r:id="rId109"/>
-    <sheet name="98_BUI_BK" sheetId="110" state="visible" r:id="rId110"/>
-    <sheet name="99_METCO-R_BK" sheetId="111" state="visible" r:id="rId111"/>
-    <sheet name="100_0169_HK" sheetId="112" state="visible" r:id="rId112"/>
-    <sheet name="Coverage" sheetId="113" state="visible" r:id="rId113"/>
-    <sheet name="References" sheetId="114" state="visible" r:id="rId114"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global_Top_100" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_NorthAmerica" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_LatinAmerica" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Core" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Nordics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Periphery" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_CEE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_Asia_Dev" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_Asia_Em" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_MEA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_088910_KQ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_AWC_SI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_2230_HK" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_0057_HK" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_003650_KS" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ZENIFIB_BO" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_SHRIDINE_BO" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_TPP_BK" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_0882_HK" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ALGEV_PA" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_6155_T" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_0100_KL" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_IRC_BK" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_JAMESWARREN_BO" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_4301_T" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_2348_HK" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_S23_SI" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_4629_T" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_1798_T" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_FPIP_ST" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_6907_T" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_014570_KQ" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_NPK_BK" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_HTMEDIA_BO" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_052330_KQ" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_120240_KQ" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_6986_T" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_035610_KQ" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_0114_HK" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_BENGALT_BO" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_SIAM_BK" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_036190_KQ" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_PRIMEPRO_BO" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_7722_T" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_METCO_BK" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_0420_HK" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_2033_HK" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_031510_KQ" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_1795_T" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_047820_KQ" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_0212_HK" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_PBMPOLY_BO" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_054800_KQ" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_015230_KS" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_0538_HK" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_0887_HK" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_7219_T" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_053980_KQ" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_TMC-R_BK" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_0018_HK" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="51_7871_T" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52_219420_KQ" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="53_CILSEC_BO" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="54_7614_T" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="55_1758_T" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="56_200570_SZ" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="57_3828_HK" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="58_HGS_BO" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="59_HGS_NS" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60_4625_T" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="61_NPK-R_BK" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="62_HMVL_BO" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="63_HMVL_NS" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64_3908_T" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="65_MANALIPETC_NS" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="66_016090_KS" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="67_7877_T" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="68_214320_KS" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="69_7851_T" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="70_4170_T" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="71_0865_HK" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72_1118_HK" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="73_HCO_PA" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="74_9625_T" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="75_BAI_SI" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="76_3054_T" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="77_SFG1T_TL" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="78_051160_KQ" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="79_0927_HK" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="80_BEC_BK" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="81_8119_T" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="82_PURPLE_BO" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="83_133750_KQ" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="84_043610_KQ" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="85_7057_T" sheetId="97" state="visible" r:id="rId97"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86_SKAKO_CO" sheetId="98" state="visible" r:id="rId98"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="87_POONADAL_BO" sheetId="99" state="visible" r:id="rId99"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="88_002758_SZ" sheetId="100" state="visible" r:id="rId100"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="89_000850_KS" sheetId="101" state="visible" r:id="rId101"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_0236_HK" sheetId="102" state="visible" r:id="rId102"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91_5MZ_SI" sheetId="103" state="visible" r:id="rId103"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92_0149_KL" sheetId="104" state="visible" r:id="rId104"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="93_3954_T" sheetId="105" state="visible" r:id="rId105"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="94_5951_T" sheetId="106" state="visible" r:id="rId106"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="95_0411_HK" sheetId="107" state="visible" r:id="rId107"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="96_7446_T" sheetId="108" state="visible" r:id="rId108"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="97_9918_HK" sheetId="109" state="visible" r:id="rId109"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="98_BUI_BK" sheetId="110" state="visible" r:id="rId110"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_METCO-R_BK" sheetId="111" state="visible" r:id="rId111"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100_0169_HK" sheetId="112" state="visible" r:id="rId112"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="113" state="visible" r:id="rId113"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="114" state="visible" r:id="rId114"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -2435,10 +2435,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>17.43024076020854</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -2930,10 +2928,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>3.78134831617187</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -3415,10 +3411,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>3.67907508468594</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -3908,10 +3902,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>3.05932472993346</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -4391,10 +4383,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>34.47785675232367</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -4870,10 +4860,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.689902831953099</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5363,10 +5351,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>1.28093043847752</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5856,10 +5842,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-5.49631583738658</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -6349,10 +6333,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.112116069337179</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -6844,10 +6826,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>2.73869571948923</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8444,10 +8424,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.80763936378434</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8937,10 +8915,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.00038199914789</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -9426,10 +9402,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>18.43843783359181</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -11607,10 +11581,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>8.95404636415233</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -12108,10 +12080,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-0.22712524334847</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -12601,10 +12571,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>32.52742891395208</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -13094,10 +13062,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>29.12052230728846</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -13589,10 +13555,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-6.109694716853889</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14078,10 +14042,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>26.21823687104556</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14569,10 +14531,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>3.69136615408451</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15168,10 +15128,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>12.07545677042703</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15651,10 +15609,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-4.85849326192409</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16152,10 +16108,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>13.16741950428538</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16649,10 +16603,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-2.05160744500846</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -17138,10 +17090,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>23.99058833898137</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -17631,10 +17581,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-2.14910060299603</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18114,10 +18062,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-2.2457207058357</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18601,10 +18547,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>24.39749694415558</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -19094,10 +19038,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>16.08568822862014</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -19599,10 +19541,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>24.03992556251057</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -24372,10 +24312,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>6.929317560577431</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -24865,10 +24803,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>15.96915285260003</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -25360,10 +25296,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>44.44050164399806</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -25845,10 +25779,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>14.66329044442543</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -26330,10 +26262,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-14.02875104746569</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -26823,10 +26753,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>13.30859566835752</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -27314,10 +27242,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>8.700165361078579</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -27807,10 +27733,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>39.39906543686433</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -28302,10 +28226,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>23.42328269392889</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -29287,12 +29209,12 @@
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>WDFN</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Woodlands Financial Services Company</t>
+          <t>IN8bio Inc. Common Stock</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -29302,7 +29224,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -29311,7 +29233,7 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>41613784</v>
+        <v>14672164</v>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
@@ -29319,7 +29241,7 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.6275356665932621</v>
+        <v>0.633707255089732</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -29328,12 +29250,12 @@
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>WDFN</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>SB Financial Group, Inc.</t>
+          <t>Woodlands Financial Services Company</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -29348,11 +29270,11 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>133408992</v>
+        <v>41613784</v>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
@@ -29360,7 +29282,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.6216880092147714</v>
+        <v>0.6275356665932621</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -29369,12 +29291,12 @@
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>SF-PB</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp.</t>
+          <t>SB Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -29389,11 +29311,11 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>1712339787.48</v>
+        <v>133408992</v>
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
@@ -29401,7 +29323,7 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.6164818952639349</v>
+        <v>0.6216880092147714</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -29410,12 +29332,12 @@
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>SF-PB</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>PCB Bancorp</t>
+          <t>Stifel Financial Corp.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -29434,7 +29356,7 @@
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>332807808</v>
+        <v>1712339787.48</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -29442,7 +29364,7 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.6151552193677089</v>
+        <v>0.6164818952639349</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -29451,12 +29373,12 @@
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Capital Bancorp, Inc.</t>
+          <t>PCB Bancorp</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -29475,7 +29397,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>488641664</v>
+        <v>332807808</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -29483,7 +29405,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.6107887984927115</v>
+        <v>0.6151552193677089</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -29492,12 +29414,12 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Expensify Inc. Class A Common Stock</t>
+          <t>Capital Bancorp, Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -29507,16 +29429,16 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>109939456</v>
+        <v>488641664</v>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -29524,7 +29446,7 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.6074663281236288</v>
+        <v>0.6107887984927115</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -29533,12 +29455,12 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>UNTC</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Unit Corporation</t>
+          <t>Expensify Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -29548,7 +29470,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -29557,15 +29479,15 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>329842272</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>109939456</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.6054823277256512</v>
+        <v>0.6074663281236288</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -29574,39 +29496,39 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>CF.TO</t>
+          <t>UNTC</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Unit Corporation</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>1298389248</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>329842272</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.6017773057481686</v>
+        <v>0.6054823277256512</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -29615,12 +29537,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>ACTG</t>
+          <t>CCB</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Acacia Research Corporation</t>
+          <t>Coastal Financial Corporation</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -29630,7 +29552,7 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29639,15 +29561,15 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>442378240</v>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>1043171008</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.5965019081647075</v>
+        <v>0.6054292644471873</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -29656,17 +29578,17 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>TSBK</t>
+          <t>CF.TO</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Timberland Bancorp, Inc.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -29680,7 +29602,7 @@
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>306542624</v>
+        <v>1298389248</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -29688,7 +29610,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.5908017213121732</v>
+        <v>0.6017773057481686</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -29697,12 +29619,12 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>TUSK</t>
+          <t>ACTG</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Mammoth Energy Services, Inc.</t>
+          <t>Acacia Research Corporation</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -29712,16 +29634,16 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>154146080</v>
+        <v>442378240</v>
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
@@ -29729,7 +29651,7 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.5887142348338045</v>
+        <v>0.5965019081647075</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -29738,31 +29660,31 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>CTX.TO</t>
+          <t>TSBK</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Crescita Therapeutics Inc.</t>
+          <t>Timberland Bancorp, Inc.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>13960454</v>
+        <v>306542624</v>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
@@ -29770,7 +29692,7 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.5851890188844633</v>
+        <v>0.5956768584011072</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -29779,12 +29701,12 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>GVFF</t>
+          <t>TUSK</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Greenville Federal Financial Corporation</t>
+          <t>Mammoth Energy Services, Inc.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -29794,24 +29716,24 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>14086171</v>
-      </c>
-      <c r="I23" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>154146080</v>
+      </c>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.5789224769242298</v>
+        <v>0.5887142348338045</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -29820,31 +29742,31 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>FXNC</t>
+          <t>CTX.TO</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>First National Corporation</t>
+          <t>Crescita Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>240218496</v>
+        <v>13960454</v>
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
@@ -29852,7 +29774,7 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.5717453185837423</v>
+        <v>0.5851890188844633</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -29861,12 +29783,12 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>OPHC</t>
+          <t>GVFF</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>OptimumBank Holdings, Inc.</t>
+          <t>Greenville Federal Financial Corporation</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -29881,19 +29803,19 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>66739896</v>
-      </c>
-      <c r="I25" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>14086171</v>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.5708335305999747</v>
+        <v>0.5789224769242298</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -29902,12 +29824,12 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>OPHC</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>IN8bio Inc. Common Stock</t>
+          <t>OptimumBank Holdings, Inc.</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -29917,24 +29839,24 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>14672164</v>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>66739896</v>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.570061492184822</v>
+        <v>0.5750975764484768</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -29943,12 +29865,12 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>AMFC</t>
+          <t>FXNC</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>AMB Financial Corp.</t>
+          <t>First National Corporation</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -29963,11 +29885,11 @@
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>30080614</v>
+        <v>240218496</v>
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
@@ -29975,7 +29897,7 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.5652887127151734</v>
+        <v>0.5717453185837423</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -29984,12 +29906,12 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>AMFC</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Grid Dynamics Holdings, Inc.</t>
+          <t>AMB Financial Corp.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -29999,16 +29921,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>561130816</v>
+        <v>30080614</v>
       </c>
       <c r="I28" s="25" t="inlineStr">
         <is>
@@ -30016,7 +29938,7 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.5614658611178881</v>
+        <v>0.5652887127151734</v>
       </c>
     </row>
   </sheetData>
@@ -30405,10 +30327,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>12.96488373879826</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -30898,10 +30818,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-1.07304976403589</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -31389,10 +31307,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>32.22922398597871</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -31882,10 +31798,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-29.29164765468225</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -32375,10 +32289,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>23.85416843924622</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -32866,10 +32778,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -33359,10 +33269,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>28.95813021275008</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -33852,10 +33760,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.00038199914789</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -34345,10 +34251,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-6.54779627873395</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -34834,10 +34738,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-10.25953389830508</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -36438,10 +36340,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>8.272729934564961</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -36931,10 +36831,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>19.00031673248309</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -37424,10 +37322,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-30.35739413704464</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -37921,10 +37817,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>26.77384147074138</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -38408,10 +38302,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-10.84555980465894</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -38901,10 +38793,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>21.56346844565357</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -39388,10 +39278,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>10.91122469934276</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -39881,10 +39769,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>6.67598367194824</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -40374,10 +40260,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>10.22818632319828</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -40867,10 +40751,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-0.3077629745327</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -42479,10 +42361,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>16.46921972294803</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -42968,10 +42848,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.887511806556289</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -43453,10 +43331,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-13.34014842701702</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -44445,10 +44321,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>36.17871968574859</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -44920,10 +44794,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-14.93020227096984</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -45413,10 +45285,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.9101608172661</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -45898,10 +45768,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>7.63524398318748</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -46391,10 +46259,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>20.73960569163904</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -46876,10 +46742,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-3.13696051919956</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -48478,10 +48342,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-5.792024276405709</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -48973,10 +48835,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-5.792024276405709</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -49466,10 +49326,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>1.86765509834559</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -49961,10 +49819,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>13.30859566835752</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -50444,10 +50300,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>10.06580694661669</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -50929,10 +50783,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>10.06580694661669</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -51414,10 +51266,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-11.46843530536362</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -51899,10 +51749,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>13.96357232031389</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -52394,10 +52242,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-6.17879992883372</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -52879,10 +52725,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-2.54040579419286</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -54485,10 +54329,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>2.16278973460767</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -54978,10 +54820,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>9.17490766711885</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -55471,10 +55311,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-3.7361378093185</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -55968,10 +55806,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>18.95329441201</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -56461,10 +56297,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>4.94241658792309</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -56946,10 +56780,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>14.44646813842066</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -57934,10 +57766,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-0.41834398926513</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -58421,10 +58251,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>11.0090502587112</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -58908,10 +58736,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-4.48424315481315</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -60504,10 +60330,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>8.359824023819741</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -60983,10 +60807,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-6.746557503569189</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -61484,10 +61306,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-10.02889608462793</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -61969,10 +61789,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>8.648901912625909</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -62947,10 +62765,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>-6.843754472601001</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -63434,10 +63250,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>2.3545238527304</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -63919,10 +63733,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>1.57321523300231</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -64907,10 +64719,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="36" t="n">
+        <v>41.00065123731966</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -122,7 +122,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="113" state="visible" r:id="rId113"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="114" state="visible" r:id="rId114"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'R_NorthAmerica'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'R_LatinAmerica'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'R_EU_Core'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'R_EU_Nordics'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'R_EU_Periphery'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'R_EU_CEE'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'R_Asia_Dev'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'R_Asia_Em'!$B$3:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'R_MEA'!$B$3:$J$28</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -2050,6 +2060,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -8075,6 +8086,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -11240,6 +11252,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -29976,6 +29989,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -35981,6 +35995,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -42000,6 +42015,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -47977,6 +47993,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -53952,6 +53969,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -59945,6 +59963,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B3:J28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -837,7 +837,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,558-equity global universe, restricted to the 18,534 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,558-equity global universe, restricted to the 18,649 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>18,534</t>
+          <t>18,649</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -1,126 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global_Top_100" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_NorthAmerica" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_LatinAmerica" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Core" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Nordics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_Periphery" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_EU_CEE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_Asia_Dev" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_Asia_Em" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R_MEA" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_088910_KQ" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_AWC_SI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_2230_HK" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_0057_HK" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_003650_KS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ZENIFIB_BO" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_ALGEV_PA" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_0882_HK" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_TPP_BK" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_SHRIDINE_BO" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_6155_T" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_0100_KL" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_IRC_BK" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_JAMESWARREN_BO" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_2348_HK" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_4301_T" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_S23_SI" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_4629_T" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_1798_T" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_6907_T" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_FPIP_ST" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_014570_KQ" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_NPK_BK" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_052330_KQ" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_HTMEDIA_BO" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_120240_KQ" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_6986_T" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_035610_KQ" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_0114_HK" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_7722_T" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_BENGALT_BO" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_SIAM_BK" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_036190_KQ" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_PRIMEPRO_BO" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_METCO_BK" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_0420_HK" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_2033_HK" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_031510_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_0538_HK" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_0212_HK" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_1795_T" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_047820_KQ" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_PBMPOLY_BO" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_054800_KQ" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_0887_HK" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_015230_KS" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_7219_T" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_053980_KQ" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_7871_T" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_TMC-R_BK" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="51_CILSEC_BO" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52_0018_HK" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="53_KROS" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="54_219420_KQ" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="55_7614_T" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="56_1758_T" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="57_200570_SZ" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="58_4625_T" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="59_3828_HK" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60_HGS_BO" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="61_HGS_NS" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="62_NPK-R_BK" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="63_HCO_PA" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64_HMVL_BO" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="65_HMVL_NS" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="66_3908_T" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="67_7877_T" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="68_016090_KS" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="69_214320_KS" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="70_1118_HK" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="71_7851_T" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72_4170_T" sheetId="84" state="visible" r:id="rId84"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="73_BAI_SI" sheetId="85" state="visible" r:id="rId85"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="74_9625_T" sheetId="86" state="visible" r:id="rId86"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="75_MANALIPETC_NS" sheetId="87" state="visible" r:id="rId87"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="76_3054_T" sheetId="88" state="visible" r:id="rId88"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="77_SFG1T_TL" sheetId="89" state="visible" r:id="rId89"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="78_0865_HK" sheetId="90" state="visible" r:id="rId90"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="79_051160_KQ" sheetId="91" state="visible" r:id="rId91"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="80_0518_HK" sheetId="92" state="visible" r:id="rId92"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="81_0927_HK" sheetId="93" state="visible" r:id="rId93"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="82_8119_T" sheetId="94" state="visible" r:id="rId94"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="83_BEC_BK" sheetId="95" state="visible" r:id="rId95"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="84_133750_KQ" sheetId="96" state="visible" r:id="rId96"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="85_043610_KQ" sheetId="97" state="visible" r:id="rId97"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86_5MZ_SI" sheetId="98" state="visible" r:id="rId98"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="87_7057_T" sheetId="99" state="visible" r:id="rId99"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="88_PURPLE_BO" sheetId="100" state="visible" r:id="rId100"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="89_SKAKO_CO" sheetId="101" state="visible" r:id="rId101"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_0411_HK" sheetId="102" state="visible" r:id="rId102"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91_POONADAL_BO" sheetId="103" state="visible" r:id="rId103"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92_3954_T" sheetId="104" state="visible" r:id="rId104"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="93_000850_KS" sheetId="105" state="visible" r:id="rId105"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="94_3020_T" sheetId="106" state="visible" r:id="rId106"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="95_0236_HK" sheetId="107" state="visible" r:id="rId107"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="96_BUI_BK" sheetId="108" state="visible" r:id="rId108"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="97_002758_SZ" sheetId="109" state="visible" r:id="rId109"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="98_5951_T" sheetId="110" state="visible" r:id="rId110"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_7446_T" sheetId="111" state="visible" r:id="rId111"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100_4976_T" sheetId="112" state="visible" r:id="rId112"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="113" state="visible" r:id="rId113"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="114" state="visible" r:id="rId114"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Global_Top_100" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="R_NorthAmerica" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="R_LatinAmerica" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="R_EU_Core" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="R_EU_Nordics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="R_EU_Periphery" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="R_EU_CEE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="R_Asia_Dev" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="R_Asia_Em" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="R_MEA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="01_088910_KQ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="02_AWC_SI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="03_2230_HK" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="04_0057_HK" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="05_003650_KS" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="06_ZENIFIB_BO" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="07_ALGEV_PA" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="08_0882_HK" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="09_TPP_BK" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="10_SHRIDINE_BO" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="11_6155_T" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="12_0100_KL" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="13_IRC_BK" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="14_JAMESWARREN_BO" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="15_2348_HK" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="16_4301_T" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="17_S23_SI" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="18_4629_T" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="19_1798_T" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="20_6907_T" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="21_FPIP_ST" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="22_014570_KQ" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="23_NPK_BK" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="24_052330_KQ" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="25_HTMEDIA_BO" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="26_120240_KQ" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="27_6986_T" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="28_035610_KQ" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="29_0114_HK" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="30_7722_T" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="31_BENGALT_BO" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="32_SIAM_BK" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="33_036190_KQ" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="34_PRIMEPRO_BO" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="35_METCO_BK" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="36_0420_HK" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="37_2033_HK" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="38_031510_KQ" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="39_0538_HK" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="40_0212_HK" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="41_1795_T" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="42_047820_KQ" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="43_PBMPOLY_BO" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="44_054800_KQ" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="45_0887_HK" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="46_015230_KS" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="47_7219_T" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="48_053980_KQ" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="49_7871_T" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="50_TMC-R_BK" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="51_CILSEC_BO" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="52_0018_HK" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="53_KROS" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="54_219420_KQ" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="55_7614_T" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="56_1758_T" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="57_200570_SZ" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="58_4625_T" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="59_3828_HK" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="60_HGS_BO" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="61_HGS_NS" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="62_NPK-R_BK" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="63_HCO_PA" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="64_HMVL_BO" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="65_HMVL_NS" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="66_3908_T" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="67_7877_T" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="68_016090_KS" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="69_214320_KS" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="70_1118_HK" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="71_7851_T" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet name="72_4170_T" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet name="73_BAI_SI" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet name="74_9625_T" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet name="75_MANALIPETC_NS" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet name="76_3054_T" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet name="77_SFG1T_TL" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet name="78_0865_HK" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet name="79_051160_KQ" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet name="80_0518_HK" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet name="81_0927_HK" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet name="82_8119_T" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet name="83_BEC_BK" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet name="84_133750_KQ" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet name="85_043610_KQ" sheetId="97" state="visible" r:id="rId97"/>
+    <sheet name="86_5MZ_SI" sheetId="98" state="visible" r:id="rId98"/>
+    <sheet name="87_7057_T" sheetId="99" state="visible" r:id="rId99"/>
+    <sheet name="88_PURPLE_BO" sheetId="100" state="visible" r:id="rId100"/>
+    <sheet name="89_SKAKO_CO" sheetId="101" state="visible" r:id="rId101"/>
+    <sheet name="90_0411_HK" sheetId="102" state="visible" r:id="rId102"/>
+    <sheet name="91_POONADAL_BO" sheetId="103" state="visible" r:id="rId103"/>
+    <sheet name="92_3954_T" sheetId="104" state="visible" r:id="rId104"/>
+    <sheet name="93_000850_KS" sheetId="105" state="visible" r:id="rId105"/>
+    <sheet name="94_3020_T" sheetId="106" state="visible" r:id="rId106"/>
+    <sheet name="95_0236_HK" sheetId="107" state="visible" r:id="rId107"/>
+    <sheet name="96_BUI_BK" sheetId="108" state="visible" r:id="rId108"/>
+    <sheet name="97_002758_SZ" sheetId="109" state="visible" r:id="rId109"/>
+    <sheet name="98_5951_T" sheetId="110" state="visible" r:id="rId110"/>
+    <sheet name="99_7446_T" sheetId="111" state="visible" r:id="rId111"/>
+    <sheet name="100_4976_T" sheetId="112" state="visible" r:id="rId112"/>
+    <sheet name="Coverage" sheetId="113" state="visible" r:id="rId113"/>
+    <sheet name="References" sheetId="114" state="visible" r:id="rId114"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'R_NorthAmerica'!$B$3:$J$28</definedName>
@@ -837,7 +837,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 25,558-equity global universe, restricted to the 18,649 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 42,600-equity global universe, restricted to the 20,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>25,558</t>
+          <t>42,600</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>18,649</t>
+          <t>20,381</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -9648,22 +9648,22 @@
         </is>
       </c>
       <c r="C5" s="46" t="n">
-        <v>25558</v>
+        <v>42600</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>25084</v>
+        <v>42119</v>
       </c>
       <c r="H5" s="47" t="n">
-        <v>1.854605211675405</v>
+        <v>1.129107981220657</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -837,7 +837,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 42,600-equity global universe, restricted to the 20,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 42,600-equity global universe, restricted to the 23,228 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>20,381</t>
+          <t>23,228</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -27718,8 +27718,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n">
-        <v>2215</v>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
@@ -55299,8 +55301,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="36" t="n">
-        <v>228.6293055592724</v>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -56503,10 +56503,8 @@
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E30" s="36" t="n">
+        <v>207.2668711656441</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 40,974-equity global universe, restricted to the 21,944 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 46,526-equity global universe, restricted to the 21,944 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>40,974</t>
+          <t>46,526</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="C5" s="45" t="n">
-        <v>40974</v>
+        <v>46526</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>130</v>
@@ -9603,10 +9603,10 @@
         <v>131</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>40512</v>
+        <v>46064</v>
       </c>
       <c r="H5" s="46" t="n">
-        <v>1.127544296383072</v>
+        <v>0.9929931651119803</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -56493,10 +56493,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="24" t="n">
+        <v>-0.6718202981877625</v>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 46,526-equity global universe, restricted to the 21,944 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 46,526-equity global universe, restricted to the 22,055 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>21,944</t>
+          <t>22,055</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -28977,12 +28977,12 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>AKRTF</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Aker Solutions ASA</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -28992,16 +28992,16 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>99749680</v>
+        <v>2162934272</v>
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         </is>
       </c>
       <c r="J7" s="24" t="n">
-        <v>0.7252912580060217</v>
+        <v>0.7296969857978951</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -29018,17 +29018,17 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>SPOT.V</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>GoldSpot Discoveries Corp.</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -29038,11 +29038,11 @@
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>40913904</v>
+        <v>99749680</v>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.7034450954971426</v>
+        <v>0.7252912580060217</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -29059,31 +29059,31 @@
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>CURN</t>
+          <t>SPOT.V</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Currency Exchange International, Corp.</t>
+          <t>GoldSpot Discoveries Corp.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>123871288</v>
+        <v>40913904</v>
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.695358805194262</v>
+        <v>0.7034450954971426</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -29100,12 +29100,12 @@
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>WHLM</t>
+          <t>CURN</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Wilhelmina International, Inc.</t>
+          <t>Currency Exchange International, Corp.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -29115,16 +29115,16 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>13086788</v>
+        <v>123871288</v>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.6946139276159645</v>
+        <v>0.695358805194262</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -29141,12 +29141,12 @@
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>WHLM</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Grid Dynamics Holdings, Inc.</t>
+          <t>Wilhelmina International, Inc.</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -29156,16 +29156,16 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>457434496</v>
+        <v>13086788</v>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.6817985002231182</v>
+        <v>0.6946139276159645</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -29182,12 +29182,12 @@
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>AAME</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Atlantic American Corporation</t>
+          <t>Grid Dynamics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -29197,24 +29197,24 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>34675288</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>457434496</v>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.6760620079072324</v>
+        <v>0.6817985002231182</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -29223,12 +29223,12 @@
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>ACTG</t>
+          <t>AAME</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Acacia Research Corporation</t>
+          <t>Atlantic American Corporation</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -29238,16 +29238,16 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>453003040</v>
+        <v>34675288</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.6752690799485772</v>
+        <v>0.6760620079072324</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -29264,12 +29264,12 @@
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>ACTG</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Hennessy Advisors, Inc.</t>
+          <t>Acacia Research Corporation</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -29279,24 +29279,24 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>81552704</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>453003040</v>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.6673368250323876</v>
+        <v>0.6752690799485772</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -29305,12 +29305,12 @@
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>TCRX</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>TScan Therapeutics Inc. Common Stock</t>
+          <t>Hennessy Advisors, Inc.</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -29320,7 +29320,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>65350816</v>
+        <v>81552704</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.6644487169711856</v>
+        <v>0.6673368250323876</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -29346,12 +29346,12 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>TCRX</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>MarketWise Inc. Class A Common Stock</t>
+          <t>TScan Therapeutics Inc. Common Stock</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -29361,7 +29361,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -29370,7 +29370,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>54794264</v>
+        <v>65350816</v>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.6623719675958988</v>
+        <v>0.6644487169711856</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -29387,39 +29387,39 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>FNC.V</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Fancamp Exploration Ltd.</t>
+          <t>MarketWise Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>36067816</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>54794264</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.6613508713507008</v>
+        <v>0.6623719675958988</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -29428,22 +29428,22 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>FNC.V</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>IN8bio Inc. Common Stock</t>
+          <t>Fancamp Exploration Ltd.</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -29452,15 +29452,15 @@
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>13041940</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>36067816</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.6289914718942511</v>
+        <v>0.6613508713507008</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -29469,12 +29469,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>SF-PB</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp.</t>
+          <t>IN8bio Inc. Common Stock</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -29484,16 +29484,16 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>1712339787.48</v>
+        <v>13041940</v>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.6226894823513184</v>
+        <v>0.6289914718942511</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -29510,12 +29510,12 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>PBSV</t>
+          <t>SF-PB</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Pharma-Bio Serv, Inc.</t>
+          <t>Stifel Financial Corp.</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -29525,16 +29525,16 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>12366914</v>
+        <v>1712339787.48</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.6212391170003443</v>
+        <v>0.6226894823513184</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -29551,12 +29551,12 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>PBSV</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Bionano Genomics, Inc.</t>
+          <t>Pharma-Bio Serv, Inc.</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -29575,7 +29575,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>12755800</v>
+        <v>12366914</v>
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.6187066960289322</v>
+        <v>0.6212391170003443</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -29592,12 +29592,12 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>GDOT</t>
+          <t>BNGO</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Green Dot Corporation</t>
+          <t>Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -29607,16 +29607,16 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>757280896</v>
+        <v>12755800</v>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.6185383768811727</v>
+        <v>0.6187066960289322</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -29633,12 +29633,12 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>GDOT</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Katapult Holdings Inc. Common Stock</t>
+          <t>Green Dot Corporation</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -29648,16 +29648,16 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>32688298</v>
+        <v>757280896</v>
       </c>
       <c r="I23" s="25" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.6167275204306412</v>
+        <v>0.6185383768811727</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -29674,12 +29674,12 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Katapult Holdings Inc. Common Stock</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -29689,16 +29689,16 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>91686464</v>
+        <v>32688298</v>
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.6149199055936468</v>
+        <v>0.6167275204306412</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -29715,12 +29715,12 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>UNTC</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Unit Corporation</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -29739,15 +29739,15 @@
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>311635904</v>
-      </c>
-      <c r="I25" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>91686464</v>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.6054823277256512</v>
+        <v>0.6149199055936468</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -29756,12 +29756,12 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>RV1.F</t>
+          <t>UNTC</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Raven Industries, Inc.</t>
+          <t>Unit Corporation</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -29771,24 +29771,24 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>1823126272</v>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>311635904</v>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.6047869889152389</v>
+        <v>0.6054823277256512</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>HOOK</t>
+          <t>RV1.F</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>HOOKIPA Pharma Inc.</t>
+          <t>Raven Industries, Inc.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -29812,16 +29812,16 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>14232977</v>
+        <v>1823126272</v>
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.6025486596891136</v>
+        <v>0.6047869889152389</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -29838,12 +29838,12 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>7060.KL</t>
+          <t>HOOK</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>New Hoong Fatt Holdings Bhd</t>
+          <t>HOOKIPA Pharma Inc.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -29853,7 +29853,7 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -29862,7 +29862,7 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>224868544</v>
+        <v>14232977</v>
       </c>
       <c r="I28" s="25" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.6019416786219631</v>
+        <v>0.6025486596891136</v>
       </c>
     </row>
   </sheetData>
@@ -56493,8 +56493,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n">
-        <v>-0.6718202981877625</v>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -55021,42 +55021,42 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>NBA.LS</t>
+          <t>R4.MC</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Novabase S.G.P.S., S.A.</t>
+          <t>Renta 4 Banco, S.A.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>306669280</v>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>777240192</v>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.3964734355710773</v>
+        <v>0.3984065238614438</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -55065,22 +55065,22 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>EYAPS.AT</t>
+          <t>NBA.LS</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Thessaloniki Water Supply &amp; Sewerage Co S.A.</t>
+          <t>Novabase S.G.P.S., S.A.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -55089,18 +55089,18 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>164257504</v>
-      </c>
-      <c r="I28" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>306669280</v>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.3944587233284998</v>
+        <v>0.3964734355710773</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -31463,12 +31463,12 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>IN8bio Inc. Common Stock</t>
+          <t>9F Inc.</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -31478,16 +31478,16 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>13041940</v>
+        <v>30610668</v>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
@@ -31495,18 +31495,16 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.7705145530704575</v>
+        <v>0.7698883687256359</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.587981</v>
-      </c>
-      <c r="M17" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.055835366</v>
+      </c>
+      <c r="M17" s="24" t="n">
+        <v>0.10559772</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -31515,12 +31513,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>SF-PB</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>9F Inc.</t>
+          <t>Stifel Financial Corp.</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -31530,16 +31528,16 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>30610668</v>
+        <v>1712339787.48</v>
       </c>
       <c r="I18" s="25" t="inlineStr">
         <is>
@@ -31547,16 +31545,16 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.7698883687256359</v>
+        <v>0.7680252075321161</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.055835366</v>
+        <v>0.6591588</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>0.10559772</v>
+        <v>0.3010436842474461</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -31565,12 +31563,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>SF-PB</t>
+          <t>TIGR</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp.</t>
+          <t>Up Fintech Holding Limited</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -31589,7 +31587,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>1712339787.48</v>
+        <v>838106112</v>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -31597,16 +31595,16 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.7680252075321161</v>
+        <v>0.7574812361405707</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.6591588</v>
+        <v>0.9904963</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>0.3010436842474461</v>
+        <v>1.4758615</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -31615,12 +31613,12 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>TIGR</t>
+          <t>XNET</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Up Fintech Holding Limited</t>
+          <t>Xunlei Ltd</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -31630,7 +31628,7 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -31639,7 +31637,7 @@
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>838106112</v>
+        <v>341184288</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -31647,16 +31645,16 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.7574812361405707</v>
+        <v>0.7557172277310804</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.9904963</v>
+        <v>0.24528648</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>1.4758615</v>
+        <v>0.6895314</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -31665,12 +31663,12 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>080010.KQ</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>eSang Networks Co.,Ltd</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -31680,16 +31678,16 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>341184288</v>
+        <v>40157934.09804344</v>
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
@@ -31697,16 +31695,16 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.7557172277310804</v>
+        <v>0.7539593481207859</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.24528648</v>
+        <v>0.4318499805098363</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.6895314</v>
+        <v>0.5690626668871859</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -31715,12 +31713,12 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>080010.KQ</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>eSang Networks Co.,Ltd</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -31739,7 +31737,7 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>40157934.09804344</v>
+        <v>91686464</v>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
@@ -31747,16 +31745,16 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.7539593481207859</v>
+        <v>0.7379038867123762</v>
       </c>
       <c r="K22" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.4318499805098363</v>
+        <v>0.8930992684661166</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>0.5690626668871859</v>
+        <v>2.52503274489824</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -31765,17 +31763,17 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>ELC.V</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Elysee Development Corp.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -31785,11 +31783,11 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>91686464</v>
+        <v>13155677.1619345</v>
       </c>
       <c r="I23" s="25" t="inlineStr">
         <is>
@@ -31797,16 +31795,16 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7379038867123762</v>
+        <v>0.7363425284206518</v>
       </c>
       <c r="K23" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.8930992684661166</v>
+        <v>0.8050134601820504</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>2.52503274489824</v>
+        <v>2.949994818357315</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -31815,31 +31813,31 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>ELC.V</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Elysee Development Corp.</t>
+          <t>Imperial Petroleum Inc./Marshall Islands</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>13155677.1619345</v>
+        <v>219738368</v>
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
@@ -31847,16 +31845,16 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7363425284206518</v>
+        <v>0.7361943217674636</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.8050134601820504</v>
+        <v>0.39409667</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>2.949994818357315</v>
+        <v>1.1527194</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -31865,12 +31863,12 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Imperial Petroleum Inc./Marshall Islands</t>
+          <t>Cronos Group Inc.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -31880,16 +31878,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>219738368</v>
+        <v>1049990336</v>
       </c>
       <c r="I25" s="25" t="inlineStr">
         <is>
@@ -31897,16 +31895,16 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7361943217674636</v>
+        <v>0.7342596256130441</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.39409667</v>
+        <v>0.98458296</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>1.1527194</v>
+        <v>6.581567</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -31915,12 +31913,12 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Cronos Group Inc.</t>
+          <t>Katapult Holdings Inc. Common Stock</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -31930,16 +31928,16 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>1049990336</v>
+        <v>32688298</v>
       </c>
       <c r="I26" s="25" t="inlineStr">
         <is>
@@ -31947,16 +31945,18 @@
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.7342596256130441</v>
+        <v>0.7298353476776207</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="L26" s="24" t="n">
-        <v>0.98458296</v>
+        <v>0.792</v>
+      </c>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M26" s="24" t="n">
-        <v>6.581567</v>
+        <v>0.10938541</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -31965,22 +31965,22 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>FNC.V</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Katapult Holdings Inc. Common Stock</t>
+          <t>Fancamp Exploration Ltd.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -31989,26 +31989,26 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>32688298</v>
-      </c>
-      <c r="I27" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>25843393.62515116</v>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7298353476776207</v>
+        <v>0.7274859584857709</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="L27" s="27" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="L27" s="24" t="n">
+        <v>0.62500006</v>
+      </c>
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
-      </c>
-      <c r="M27" s="24" t="n">
-        <v>0.10938541</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -32017,50 +32017,48 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>FNC.V</t>
+          <t>OPBK</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Fancamp Exploration Ltd.</t>
+          <t>OP Bancorp</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>25843393.62515116</v>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>229222336</v>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.7274859584857709</v>
+        <v>0.7274389476177404</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.62500006</v>
-      </c>
-      <c r="M28" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9850231</v>
+      </c>
+      <c r="M28" s="24" t="n">
+        <v>2.4451687</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,011 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>19,011</t>
+          <t>19,381</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -45218,17 +45218,17 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>KWG.DE</t>
+          <t>MANO.L</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>KHD Humboldt Wedag International AG</t>
+          <t>Manolete Partners Plc</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -45238,11 +45238,11 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>99223617.35094452</v>
+        <v>21086340.18307722</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -45250,13 +45250,13 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7021930682607028</v>
+        <v>0.7034140857647195</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.8177573371374227</v>
+        <v>38.42049</v>
       </c>
       <c r="M23" s="27" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         </is>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0.4832858443587639</v>
+        <v>0.5657692600000001</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -45273,12 +45273,12 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>NOEJ.DE</t>
+          <t>KWG.DE</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>NORMA Group SE</t>
+          <t>KHD Humboldt Wedag International AG</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -45293,11 +45293,11 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>562552263.8517151</v>
+        <v>99223617.35094452</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -45305,19 +45305,21 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.6951586899729738</v>
+        <v>0.7021930682607028</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.62168586</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.8177573371374227</v>
+      </c>
+      <c r="M24" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>0.59989953</v>
+        <v>0.4832858443587639</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -45326,17 +45328,17 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>ALNSC.PA</t>
+          <t>NOEJ.DE</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>NSC Groupe SA</t>
+          <t>NORMA Group SE</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -45346,11 +45348,11 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>32721293.47121429</v>
+        <v>562552263.8517151</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -45358,21 +45360,19 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.6875963988690323</v>
+        <v>0.6951586899729738</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.7812936573538326</v>
-      </c>
-      <c r="M25" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.62168586</v>
+      </c>
+      <c r="M25" s="25" t="n">
+        <v>0.8200000000000001</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>0.399147996959545</v>
+        <v>0.59989953</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -45381,29 +45381,31 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>ALNSC.PA</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Lakefront Biotherapeutics American Depositary Shares</t>
+          <t>NSC Groupe SA</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>1975014784</v>
+        <v>32721293.47121429</v>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
@@ -45411,13 +45413,13 @@
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.6845911553255807</v>
+        <v>0.6875963988690323</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.538</v>
+        <v>1</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.6070675610421075</v>
+        <v>0.7812936573538326</v>
       </c>
       <c r="M26" s="27" t="inlineStr">
         <is>
@@ -45425,7 +45427,7 @@
         </is>
       </c>
       <c r="N26" s="24" t="n">
-        <v>1.892226107351172</v>
+        <v>0.399147996959545</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -45434,31 +45436,29 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>DTW1.F</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Shearwater Group plc</t>
+          <t>Lakefront Biotherapeutics American Depositary Shares</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v/>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>12429068.02478313</v>
+        <v>1975014784</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -45466,13 +45466,13 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.6756235807596845</v>
+        <v>0.6845911553255807</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.833</v>
+        <v>0.538</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.2342750565512441</v>
+        <v>0.6070675610421075</v>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         </is>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.4756891754626153</v>
+        <v>1.892226107351172</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -45489,17 +45489,17 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>DGV.MI</t>
+          <t>DTW1.F</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Shearwater Group plc</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -45509,11 +45509,11 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>342440851.2008972</v>
+        <v>12429068.02478313</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -45521,19 +45521,21 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.6652241968985336</v>
+        <v>0.6756235807596845</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.2836072</v>
-      </c>
-      <c r="M28" s="25" t="n">
-        <v>2.76</v>
+        <v>0.2342750565512441</v>
+      </c>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.4634915</v>
+        <v>0.4756891754626153</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,385 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>19,381</t>
+          <t>19,385</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -9143,8 +9143,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
-        <v>306.7585334398339</v>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -11255,10 +11257,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.6299717839683909</v>
+        <v>0.6408275174562684</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>0.4002144241081388</v>
@@ -11268,8 +11270,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N9" s="24" t="n">
-        <v>1990.551971425654</v>
+      <c r="N9" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -31880,12 +31884,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>TCRX</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>TScan Therapeutics Inc. Common Stock</t>
+          <t>Grid Dynamics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -31895,16 +31899,16 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>65350816</v>
+        <v>457434496</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -31912,21 +31916,19 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.8028533847162836</v>
+        <v>0.8000223601618068</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.875</v>
+        <v>0.667</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.5307766704839876</v>
-      </c>
-      <c r="M11" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.862232</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>6.329376852300242</v>
+        <v>1.1008936</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -31935,12 +31937,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Grid Dynamics Holdings, Inc.</t>
+          <t>Neuphoria Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31950,16 +31952,16 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>457434496</v>
+        <v>24698798</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31967,19 +31969,21 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.8000223601618068</v>
+        <v>0.7983932004447344</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.862232</v>
-      </c>
-      <c r="M12" s="25" t="n">
-        <v>0</v>
+        <v>0.83516085</v>
+      </c>
+      <c r="M12" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N12" s="24" t="n">
-        <v>1.1008936</v>
+        <v>1.578253622747588</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31988,12 +31992,12 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics Inc.</t>
+          <t>MarketWise Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -32003,16 +32007,16 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>24698798</v>
+        <v>54794264</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -32020,13 +32024,15 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.7983932004447344</v>
+        <v>0.7924618220317332</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>0.83516085</v>
+        <v>0.857</v>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M13" s="27" t="inlineStr">
         <is>
@@ -32034,7 +32040,7 @@
         </is>
       </c>
       <c r="N13" s="24" t="n">
-        <v>1.578253622747588</v>
+        <v>0.1703568665978535</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -32043,12 +32049,12 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>VIOT</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>MarketWise Inc. Class A Common Stock</t>
+          <t>Viomi Technology Co., Ltd</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -32067,7 +32073,7 @@
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>54794264</v>
+        <v>53857384</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -32075,23 +32081,21 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.7948463611150786</v>
+        <v>0.7905415041774707</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="L14" s="27" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24" t="n">
+        <v>0.23885411</v>
+      </c>
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="N14" s="24" t="n">
-        <v>0.1703568665978535</v>
+        <v>0.022179725</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -32100,12 +32104,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>VIOT</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Viomi Technology Co., Ltd</t>
+          <t>Hennessy Advisors, Inc.</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -32115,7 +32119,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -32124,7 +32128,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>53857384</v>
+        <v>81552704</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -32132,21 +32136,19 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.7905415041774707</v>
+        <v>0.7830530304930036</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.23885411</v>
-      </c>
-      <c r="M15" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8153591</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>5.33474491040843</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.022179725</v>
+        <v>2.47077</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32155,12 +32157,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Hennessy Advisors, Inc.</t>
+          <t>9F Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32170,7 +32172,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -32179,7 +32181,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>81552704</v>
+        <v>30610668</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -32187,19 +32189,21 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.7830530304930036</v>
+        <v>0.7698883687256359</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.8153591</v>
-      </c>
-      <c r="M16" s="25" t="n">
-        <v>5.33474491040843</v>
+        <v>0.055835366</v>
+      </c>
+      <c r="M16" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>2.47077</v>
+        <v>0.10559772</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32261,12 +32265,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>TIGR</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>9F Inc.</t>
+          <t>Up Fintech Holding Limited</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32276,16 +32280,16 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>30610668</v>
+        <v>838106112</v>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
@@ -32293,13 +32297,13 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.7578967578021879</v>
+        <v>0.7574812361405707</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.055835366</v>
+        <v>0.9904963</v>
       </c>
       <c r="M18" s="27" t="inlineStr">
         <is>
@@ -32307,7 +32311,7 @@
         </is>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.10559772</v>
+        <v>1.4758615</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32316,12 +32320,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>TIGR</t>
+          <t>XNET</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Up Fintech Holding Limited</t>
+          <t>Xunlei Ltd</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -32331,7 +32335,7 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -32340,7 +32344,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>838106112</v>
+        <v>341184288</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -32348,13 +32352,13 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.7574812361405707</v>
+        <v>0.7557172277310804</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.9904963</v>
+        <v>0.24528648</v>
       </c>
       <c r="M19" s="27" t="inlineStr">
         <is>
@@ -32362,7 +32366,7 @@
         </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>1.4758615</v>
+        <v>0.6895314</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -32371,12 +32375,12 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>080010.KQ</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>eSang Networks Co.,Ltd</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -32386,16 +32390,16 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>341184288</v>
+        <v>40157934.09804344</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -32403,13 +32407,13 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.7557172277310804</v>
+        <v>0.7539593481207859</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.24528648</v>
+        <v>0.4318499805098363</v>
       </c>
       <c r="M20" s="27" t="inlineStr">
         <is>
@@ -32417,7 +32421,7 @@
         </is>
       </c>
       <c r="N20" s="24" t="n">
-        <v>0.6895314</v>
+        <v>0.5690626668871859</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -32426,12 +32430,12 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>080010.KQ</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>eSang Networks Co.,Ltd</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -32450,7 +32454,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>40157934.09804344</v>
+        <v>91686464</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -32458,13 +32462,13 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.7539593481207859</v>
+        <v>0.7379038867123762</v>
       </c>
       <c r="K21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.4318499805098363</v>
+        <v>0.8930992684661166</v>
       </c>
       <c r="M21" s="27" t="inlineStr">
         <is>
@@ -32472,7 +32476,7 @@
         </is>
       </c>
       <c r="N21" s="24" t="n">
-        <v>0.5690626668871859</v>
+        <v>2.52503274489824</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -32481,31 +32485,31 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>ELC.V</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Imperial Petroleum Inc./Marshall Islands</t>
+          <t>Elysee Development Corp.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>219738368</v>
+        <v>13155677.1619345</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -32513,13 +32517,13 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.7384568277930423</v>
+        <v>0.7363425284206518</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.39409667</v>
+        <v>0.8050134601820504</v>
       </c>
       <c r="M22" s="27" t="inlineStr">
         <is>
@@ -32527,7 +32531,7 @@
         </is>
       </c>
       <c r="N22" s="24" t="n">
-        <v>1.1527194</v>
+        <v>2.949994818357315</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -32536,12 +32540,12 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Imperial Petroleum Inc./Marshall Islands</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -32551,7 +32555,7 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -32560,7 +32564,7 @@
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>91686464</v>
+        <v>219738368</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -32568,13 +32572,13 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7379038867123762</v>
+        <v>0.7361943217674636</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.8930992684661166</v>
+        <v>0.39409667</v>
       </c>
       <c r="M23" s="27" t="inlineStr">
         <is>
@@ -32582,7 +32586,7 @@
         </is>
       </c>
       <c r="N23" s="24" t="n">
-        <v>2.52503274489824</v>
+        <v>1.1527194</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -32591,31 +32595,31 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>ELC.V</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Elysee Development Corp.</t>
+          <t>Cronos Group Inc.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>13155677.1619345</v>
+        <v>1049990336</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -32623,13 +32627,13 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7363425284206518</v>
+        <v>0.7342596256130441</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.8050134601820504</v>
+        <v>0.98458296</v>
       </c>
       <c r="M24" s="27" t="inlineStr">
         <is>
@@ -32637,7 +32641,7 @@
         </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>2.949994818357315</v>
+        <v>6.581567</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -32646,12 +32650,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Cronos Group Inc.</t>
+          <t>Katapult Holdings Inc. Common Stock</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -32661,16 +32665,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1049990336</v>
+        <v>32688298</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -32678,13 +32682,15 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7342596256130441</v>
+        <v>0.7298353476776207</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="L25" s="24" t="n">
-        <v>0.98458296</v>
+        <v>0.792</v>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M25" s="27" t="inlineStr">
         <is>
@@ -32692,7 +32698,7 @@
         </is>
       </c>
       <c r="N25" s="24" t="n">
-        <v>6.581567</v>
+        <v>0.10938541</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -32701,22 +32707,22 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>FNC.V</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Katapult Holdings Inc. Common Stock</t>
+          <t>Fancamp Exploration Ltd.</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -32725,31 +32731,31 @@
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>32688298</v>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>25843393.62515116</v>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.7298353476776207</v>
+        <v>0.7274859584857709</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="L26" s="27" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="L26" s="24" t="n">
+        <v>0.62500006</v>
+      </c>
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M26" s="27" t="inlineStr">
+      <c r="N26" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
-      </c>
-      <c r="N26" s="24" t="n">
-        <v>0.10938541</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -32758,55 +32764,51 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>FNC.V</t>
+          <t>OPBK</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Fancamp Exploration Ltd.</t>
+          <t>OP Bancorp</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>25843393.62515116</v>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>229222336</v>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7274859584857709</v>
+        <v>0.7274389476177404</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.62500006</v>
-      </c>
-      <c r="M27" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N27" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9850231</v>
+      </c>
+      <c r="M27" s="25" t="n">
+        <v>3.53787792282389</v>
+      </c>
+      <c r="N27" s="24" t="n">
+        <v>2.4451687</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -32815,12 +32817,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>OPBK</t>
+          <t>RV1.F</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>OP Bancorp</t>
+          <t>Raven Industries, Inc.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -32830,16 +32832,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>229222336</v>
+        <v>2103769133.727905</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -32847,19 +32849,21 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.7274389476177404</v>
+        <v>0.7257443866982866</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.9850231</v>
-      </c>
-      <c r="M28" s="25" t="n">
-        <v>3.53787792282389</v>
+        <v>4.638998147582697</v>
+      </c>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N28" s="24" t="n">
-        <v>2.4451687</v>
+        <v>1.41657052991453</v>
       </c>
     </row>
   </sheetData>
@@ -39574,8 +39578,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
-        <v>1453.539401863697</v>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -45849,8 +45855,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n">
-        <v>-0.6718202981877625</v>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -60673,8 +60681,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
-        <v>232.6054641204179</v>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -64637,31 +64647,29 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>9R1.F</t>
+          <t>0CKA.F</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Amica S.A.</t>
+          <t>CIG Pannonia Eletbiztosito Nyrt</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v/>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>93657838.26387404</v>
+        <v>91070365.29719923</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -64669,13 +64677,13 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.5137387991213774</v>
+        <v>0.5228390951334086</v>
       </c>
       <c r="K27" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.07579742248785951</v>
+        <v>0.0030451663386966</v>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
@@ -64683,7 +64691,7 @@
         </is>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.0338140565762613</v>
+        <v>0.0024636815883124</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -64692,12 +64700,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>01R.F</t>
+          <t>9R1.F</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>DataWalk S.A.</t>
+          <t>Amica S.A.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -64707,16 +64715,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>202894241.5393296</v>
+        <v>93657838.26387404</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -64724,13 +64732,13 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.5101108779875184</v>
+        <v>0.5137387991213774</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>2.546683815648446</v>
+        <v>0.07579742248785951</v>
       </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
@@ -64738,7 +64746,7 @@
         </is>
       </c>
       <c r="N28" s="24" t="n">
-        <v>6.200519942165956</v>
+        <v>0.0338140565762613</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,385 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>19,385</t>
+          <t>19,381</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,381 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,385 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>19,381</t>
+          <t>19,385</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -11257,10 +11257,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.6408275174562684</v>
+        <v>0.6299717839683909</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>0.4002144241081388</v>
@@ -64647,29 +64647,31 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>0CKA.F</t>
+          <t>9R1.F</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>CIG Pannonia Eletbiztosito Nyrt</t>
+          <t>Amica S.A.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v/>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>91070365.29719923</v>
+        <v>93657838.26387404</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -64677,13 +64679,13 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.5228390951334086</v>
+        <v>0.5137387991213774</v>
       </c>
       <c r="K27" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.0030451663386966</v>
+        <v>0.07579742248785951</v>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
@@ -64691,7 +64693,7 @@
         </is>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.0024636815883124</v>
+        <v>0.0338140565762613</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -64700,12 +64702,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>9R1.F</t>
+          <t>01R.F</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Amica S.A.</t>
+          <t>DataWalk S.A.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -64715,16 +64717,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>93657838.26387404</v>
+        <v>202894241.5393296</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -64732,13 +64734,13 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.5137387991213774</v>
+        <v>0.5101108779875184</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.07579742248785951</v>
+        <v>2.546683815648446</v>
       </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
@@ -64746,7 +64748,7 @@
         </is>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.0338140565762613</v>
+        <v>6.200519942165956</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -834,7 +834,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,385 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
+          <t>This book documents the top-100 nano/micro/small-cap candidates from a 36,197-equity global universe, restricted to the 19,383 names tagged by financedatabase as Nano Cap, Micro Cap or Small Cap (broadly, market caps below ~$2B). Yartseva (2025) finds the EV&lt;$250M segment delivered 37.7% annualised excess returns over 2009–2024 vs 9.7% for large-caps — a ~28-point edge that survives controls for valuation, profitability and macro factors. Alta Fox (2020) corroborates: 84% of their 350%+ TSR 5-year sample ended below $2B. We rank within the size-filtered universe using the same entry-today asymmetry score that drives the master Harvard workbook, then carve out per-region Top 25 tabs so smaller geographies aren't crowded out by US/UK/JP names.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>19,385</t>
+          <t>19,383</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -31884,12 +31884,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>TCRX</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Grid Dynamics Holdings, Inc.</t>
+          <t>TScan Therapeutics Inc. Common Stock</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -31899,16 +31899,16 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>457434496</v>
+        <v>65350816</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -31916,19 +31916,21 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.8000223601618068</v>
+        <v>0.8028533847162836</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.667</v>
+        <v>0.875</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.862232</v>
-      </c>
-      <c r="M11" s="25" t="n">
-        <v>0</v>
+        <v>0.5307766704839876</v>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N11" s="24" t="n">
-        <v>1.1008936</v>
+        <v>6.329376852300242</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -31937,12 +31939,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics Inc.</t>
+          <t>Grid Dynamics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31952,16 +31954,16 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>24698798</v>
+        <v>457434496</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31969,21 +31971,19 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.7983932004447344</v>
+        <v>0.8000223601618068</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.83516085</v>
-      </c>
-      <c r="M12" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.862232</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>1.578253622747588</v>
+        <v>1.1008936</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31992,12 +31992,12 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>MarketWise Inc. Class A Common Stock</t>
+          <t>Neuphoria Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -32007,16 +32007,16 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>54794264</v>
+        <v>24698798</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -32024,23 +32024,21 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.7924618220317332</v>
+        <v>0.7983932004447344</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="L13" s="27" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>0.83516085</v>
+      </c>
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M13" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="N13" s="24" t="n">
-        <v>0.1703568665978535</v>
+        <v>1.578253622747588</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -32049,12 +32047,12 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>VIOT</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Viomi Technology Co., Ltd</t>
+          <t>MarketWise Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -32073,7 +32071,7 @@
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>53857384</v>
+        <v>54794264</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -32081,13 +32079,15 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.7905415041774707</v>
+        <v>0.7924618220317332</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>0.23885411</v>
+        <v>0.857</v>
+      </c>
+      <c r="L14" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M14" s="27" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.022179725</v>
+        <v>0.1703568665978535</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -32104,12 +32104,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>VIOT</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Hennessy Advisors, Inc.</t>
+          <t>Viomi Technology Co., Ltd</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -32128,7 +32128,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>81552704</v>
+        <v>53857384</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -32136,19 +32136,21 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.7830530304930036</v>
+        <v>0.7905415041774707</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.8153591</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>5.33474491040843</v>
+        <v>0.23885411</v>
+      </c>
+      <c r="M15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N15" s="24" t="n">
-        <v>2.47077</v>
+        <v>0.022179725</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32157,12 +32159,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>9F Inc.</t>
+          <t>Hennessy Advisors, Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32172,7 +32174,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -32181,7 +32183,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>30610668</v>
+        <v>81552704</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -32189,21 +32191,19 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.7698883687256359</v>
+        <v>0.7830530304930036</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.055835366</v>
-      </c>
-      <c r="M16" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8153591</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <v>5.33474491040843</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.10559772</v>
+        <v>2.47077</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32212,12 +32212,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>SF-PB</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp.</t>
+          <t>9F Inc.</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32227,16 +32227,16 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>1712339787.48</v>
+        <v>30610668</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -32244,19 +32244,21 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.7680252075321161</v>
+        <v>0.7698883687256359</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.6591588</v>
-      </c>
-      <c r="M17" s="25" t="n">
-        <v>6.87</v>
+        <v>0.055835366</v>
+      </c>
+      <c r="M17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.3010436842474461</v>
+        <v>0.10559772</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32265,12 +32267,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>TIGR</t>
+          <t>SF-PB</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Up Fintech Holding Limited</t>
+          <t>Stifel Financial Corp.</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32289,7 +32291,7 @@
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>838106112</v>
+        <v>1712339787.48</v>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
@@ -32297,21 +32299,19 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.7574812361405707</v>
+        <v>0.7680252075321161</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.9904963</v>
-      </c>
-      <c r="M18" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.6591588</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <v>6.87</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>1.4758615</v>
+        <v>0.3010436842474461</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32320,12 +32320,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>TIGR</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>Up Fintech Holding Limited</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -32344,7 +32344,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>341184288</v>
+        <v>838106112</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -32352,13 +32352,13 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.7557172277310804</v>
+        <v>0.7574812361405707</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.24528648</v>
+        <v>0.9904963</v>
       </c>
       <c r="M19" s="27" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>0.6895314</v>
+        <v>1.4758615</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -32375,12 +32375,12 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>080010.KQ</t>
+          <t>XNET</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>eSang Networks Co.,Ltd</t>
+          <t>Xunlei Ltd</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -32390,16 +32390,16 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>40157934.09804344</v>
+        <v>341184288</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -32407,13 +32407,13 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.7539593481207859</v>
+        <v>0.7557172277310804</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.4318499805098363</v>
+        <v>0.24528648</v>
       </c>
       <c r="M20" s="27" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         </is>
       </c>
       <c r="N20" s="24" t="n">
-        <v>0.5690626668871859</v>
+        <v>0.6895314</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -32430,12 +32430,12 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>080010.KQ</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>eSang Networks Co.,Ltd</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -32454,7 +32454,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>91686464</v>
+        <v>40157934.09804344</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -32462,13 +32462,13 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.7379038867123762</v>
+        <v>0.7539593481207859</v>
       </c>
       <c r="K21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.8930992684661166</v>
+        <v>0.4318499805098363</v>
       </c>
       <c r="M21" s="27" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="N21" s="24" t="n">
-        <v>2.52503274489824</v>
+        <v>0.5690626668871859</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -32485,17 +32485,17 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>ELC.V</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Elysee Development Corp.</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -32505,11 +32505,11 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>13155677.1619345</v>
+        <v>91686464</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -32517,13 +32517,13 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.7363425284206518</v>
+        <v>0.7379038867123762</v>
       </c>
       <c r="K22" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.8050134601820504</v>
+        <v>0.8930992684661166</v>
       </c>
       <c r="M22" s="27" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="N22" s="24" t="n">
-        <v>2.949994818357315</v>
+        <v>2.52503274489824</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -32540,31 +32540,31 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>ELC.V</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Imperial Petroleum Inc./Marshall Islands</t>
+          <t>Elysee Development Corp.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>219738368</v>
+        <v>13155677.1619345</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -32572,13 +32572,13 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7361943217674636</v>
+        <v>0.7363425284206518</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.39409667</v>
+        <v>0.8050134601820504</v>
       </c>
       <c r="M23" s="27" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         </is>
       </c>
       <c r="N23" s="24" t="n">
-        <v>1.1527194</v>
+        <v>2.949994818357315</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -32595,12 +32595,12 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Cronos Group Inc.</t>
+          <t>Imperial Petroleum Inc./Marshall Islands</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -32610,16 +32610,16 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>1049990336</v>
+        <v>219738368</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -32627,13 +32627,13 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7342596256130441</v>
+        <v>0.7361943217674636</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.98458296</v>
+        <v>0.39409667</v>
       </c>
       <c r="M24" s="27" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>6.581567</v>
+        <v>1.1527194</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -32650,12 +32650,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Katapult Holdings Inc. Common Stock</t>
+          <t>Cronos Group Inc.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -32665,16 +32665,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>32688298</v>
+        <v>1049990336</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -32682,23 +32682,21 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7298353476776207</v>
+        <v>0.7342596256130441</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="L25" s="27" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="L25" s="24" t="n">
+        <v>0.98458296</v>
+      </c>
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M25" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="N25" s="24" t="n">
-        <v>0.10938541</v>
+        <v>6.581567</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -32707,22 +32705,22 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>FNC.V</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Fancamp Exploration Ltd.</t>
+          <t>Katapult Holdings Inc. Common Stock</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -32731,31 +32729,31 @@
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>25843393.62515116</v>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>32688298</v>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.7274859584857709</v>
+        <v>0.7298353476776207</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L26" s="24" t="n">
-        <v>0.62500006</v>
+        <v>0.792</v>
+      </c>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M26" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N26" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N26" s="24" t="n">
+        <v>0.10938541</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -32764,51 +32762,55 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>OPBK</t>
+          <t>FNC.V</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>OP Bancorp</t>
+          <t>Fancamp Exploration Ltd.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>229222336</v>
-      </c>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>25843393.62515116</v>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7274389476177404</v>
+        <v>0.7274859584857709</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.9850231</v>
-      </c>
-      <c r="M27" s="25" t="n">
-        <v>3.53787792282389</v>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>2.4451687</v>
+        <v>0.62500006</v>
+      </c>
+      <c r="M27" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N27" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -32817,12 +32819,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>RV1.F</t>
+          <t>OPBK</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Raven Industries, Inc.</t>
+          <t>OP Bancorp</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -32832,16 +32834,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>2103769133.727905</v>
+        <v>229222336</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -32849,21 +32851,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.7257443866982866</v>
+        <v>0.7274389476177404</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>4.638998147582697</v>
-      </c>
-      <c r="M28" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9850231</v>
+      </c>
+      <c r="M28" s="25" t="n">
+        <v>3.53787792282389</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>1.41657052991453</v>
+        <v>2.4451687</v>
       </c>
     </row>
   </sheetData>
@@ -38342,8 +38342,10 @@
       <c r="L12" s="24" t="n">
         <v>0.29981923</v>
       </c>
-      <c r="M12" s="25" t="n">
-        <v>48.209998</v>
+      <c r="M12" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N12" s="24" t="n">
         <v>0.084430486</v>
@@ -50310,10 +50312,8 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E29" s="24" t="n">
+        <v>-8.977983487615711</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -10476,16 +10476,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -32124,12 +32124,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Hennessy Advisors, Inc.</t>
+          <t>Neuphoria Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32139,16 +32139,16 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>80624984</v>
+        <v>20375158</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -32156,19 +32156,21 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.801267596024166</v>
+        <v>0.7985383481971811</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.7970618</v>
-      </c>
-      <c r="M17" s="25" t="n">
-        <v>5.33474491040843</v>
+        <v>0.688962</v>
+      </c>
+      <c r="M17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>2.4180484</v>
+        <v>1.578253622747588</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32177,12 +32179,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>ACTG</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics Inc.</t>
+          <t>Acacia Research Corporation</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32192,38 +32194,36 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>20375158</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>443044096</v>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.7985383481971811</v>
+        <v>0.7978305871255087</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.8</v>
+        <v>0.995</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.688962</v>
-      </c>
-      <c r="M18" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8410523</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>1.578253622747588</v>
+        <v>1.5915426</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32232,12 +32232,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>ACTG</t>
+          <t>RV1.F</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Acacia Research Corporation</t>
+          <t>Raven Industries, Inc.</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -32256,27 +32256,27 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>443044096</v>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>2481246551.957886</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.7978305871255087</v>
+        <v>0.787461511324353</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.995</v>
+        <v>0.85</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.8410523</v>
+        <v>5.6012883</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>0</v>
+        <v>2.4400001</v>
       </c>
       <c r="N19" s="24" t="n">
-        <v>1.5915426</v>
+        <v>1.6451783</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -32285,31 +32285,31 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>RV1.F</t>
+          <t>SPOT.V</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Raven Industries, Inc.</t>
+          <t>GoldSpot Discoveries Corp.</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>2481246551.957886</v>
+        <v>32853827.51483989</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -32317,19 +32317,21 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.787461511324353</v>
+        <v>0.7808553959703856</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.85</v>
+        <v>0.651</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>5.6012883</v>
-      </c>
-      <c r="M20" s="25" t="n">
-        <v>2.4400001</v>
+        <v>0.63352823</v>
+      </c>
+      <c r="M20" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N20" s="24" t="n">
-        <v>1.6451783</v>
+        <v>3.6421437</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -32338,31 +32340,31 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>SPOT.V</t>
+          <t>HERE</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>GoldSpot Discoveries Corp.</t>
+          <t>Quantasing Group Limited</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>32853827.51483989</v>
+        <v>103874616</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -32370,13 +32372,13 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.7808553959703856</v>
+        <v>0.7794728688851164</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.651</v>
+        <v>0.764</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.63352823</v>
+        <v>0.8565221</v>
       </c>
       <c r="M21" s="27" t="inlineStr">
         <is>
@@ -32384,7 +32386,7 @@
         </is>
       </c>
       <c r="N21" s="24" t="n">
-        <v>3.6421437</v>
+        <v>0.09556232000000001</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -32393,12 +32395,12 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>HERE</t>
+          <t>OPBK</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Quantasing Group Limited</t>
+          <t>OP Bancorp</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -32408,7 +32410,7 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -32417,7 +32419,7 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>103874616</v>
+        <v>230858224</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -32425,21 +32427,19 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.7794728688851164</v>
+        <v>0.7794514697914465</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.764</v>
+        <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.8565221</v>
-      </c>
-      <c r="M22" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9669752</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>3.53787792282389</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>0.09556232000000001</v>
+        <v>2.3767962</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -32448,12 +32448,12 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>OPBK</t>
+          <t>NOAH</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>OP Bancorp</t>
+          <t>Noah Holdings Ltd</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -32468,11 +32468,11 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>230858224</v>
+        <v>578683776</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -32480,19 +32480,19 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7794514697914465</v>
+        <v>0.7774229415579383</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.9669752</v>
+        <v>0.41539234</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>3.53787792282389</v>
+        <v>6.92</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>2.3767962</v>
+        <v>0.22156554</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -32501,12 +32501,12 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>NOAH</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Noah Holdings Ltd</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -32516,16 +32516,16 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>578683776</v>
+        <v>52732928</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -32533,19 +32533,21 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7774229415579383</v>
+        <v>0.7772382281821867</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.9419999999999999</v>
+        <v>1</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.41539234</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>6.92</v>
+        <v>0.78786975</v>
+      </c>
+      <c r="M24" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>0.22156554</v>
+        <v>2.7442198</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -32554,12 +32556,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>GDOT</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Green Dot Corporation</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -32569,16 +32571,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>52732928</v>
+        <v>759612416</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -32586,13 +32588,13 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7772382281821867</v>
+        <v>0.7635526072015121</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>1</v>
+        <v>0.761</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.78786975</v>
+        <v>0.80861384</v>
       </c>
       <c r="M25" s="27" t="inlineStr">
         <is>
@@ -32600,7 +32602,7 @@
         </is>
       </c>
       <c r="N25" s="24" t="n">
-        <v>2.7442198</v>
+        <v>0.33199</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -32609,12 +32611,12 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>7060.KL</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Imperial Petroleum Inc./Marshall Islands</t>
+          <t>New Hoong Fatt Holdings Bhd</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -32629,11 +32631,11 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>239180240</v>
+        <v>53759979.84742952</v>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
@@ -32641,21 +32643,19 @@
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.7675520029882157</v>
+        <v>0.758330402567876</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.957</v>
+        <v>1</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.4289653</v>
-      </c>
-      <c r="M26" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.36964437</v>
+      </c>
+      <c r="M26" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>1.2547089</v>
+        <v>0.93600476</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -32664,12 +32664,12 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>GDOT</t>
+          <t>HOOK</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Green Dot Corporation</t>
+          <t>HOOKIPA Pharma Inc.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -32679,16 +32679,16 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>759612416</v>
+        <v>14232977</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7635526072015121</v>
+        <v>0.7538404842957074</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.80861384</v>
+        <v>0.4961991702691395</v>
       </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         </is>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.33199</v>
+        <v>0.9580625336564352</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -32719,12 +32719,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>7060.KL</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>New Hoong Fatt Holdings Bhd</t>
+          <t>Huize Holding Limited</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -32734,7 +32734,7 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -32743,7 +32743,7 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>53759979.84742952</v>
+        <v>14855932</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -32751,19 +32751,23 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.758330402567876</v>
+        <v>0.7488690475248976</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.36964437</v>
-      </c>
-      <c r="M28" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>0.93600476</v>
+        <v>0.2310821</v>
+      </c>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N28" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -37918,12 +37922,12 @@
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>BGIP4.SA</t>
+          <t>MTSA4.SA</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Banco do Estado de Sergipe S.A.</t>
+          <t>METISA Metalurgica Timboense S.A.</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
@@ -37933,7 +37937,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -37942,7 +37946,7 @@
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>150829139.5280972</v>
+        <v>76408045.14136791</v>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
@@ -37950,19 +37954,19 @@
         </is>
       </c>
       <c r="J6" s="24" t="n">
-        <v>0.6593785615744231</v>
+        <v>0.6413462079248714</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="24" t="n">
-        <v>0.7756713</v>
+        <v>0.85097474</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>11.9399995</v>
+        <v>9.4</v>
       </c>
       <c r="N6" s="24" t="n">
-        <v>1.0391467</v>
+        <v>0.7923743</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -37971,12 +37975,12 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>MTSA4.SA</t>
+          <t>JALL3.SA</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>METISA Metalurgica Timboense S.A.</t>
+          <t>Jalles Machado S/A</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -37986,36 +37990,36 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>76408045.14136791</v>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>154161319.019866</v>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J7" s="24" t="n">
-        <v>0.6413462079248714</v>
+        <v>0.5990828040036182</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
       <c r="L7" s="24" t="n">
-        <v>0.85097474</v>
+        <v>0.4142657</v>
       </c>
       <c r="M7" s="25" t="n">
-        <v>9.4</v>
+        <v>0.3</v>
       </c>
       <c r="N7" s="24" t="n">
-        <v>0.7923743</v>
+        <v>0.4042455</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -38024,12 +38028,12 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>JALL3.SA</t>
+          <t>ALLD3.SA</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Jalles Machado S/A</t>
+          <t>Allied Tecnologia S.A.</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
@@ -38039,7 +38043,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -38048,7 +38052,7 @@
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>154161319.019866</v>
+        <v>95719928.2231722</v>
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
@@ -38056,19 +38060,21 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.5990828040036182</v>
+        <v>0.5967054981809672</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>0.4142657</v>
-      </c>
-      <c r="M8" s="25" t="n">
-        <v>0.3</v>
+        <v>0.31638625</v>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N8" s="24" t="n">
-        <v>0.4042455</v>
+        <v>0.09002446</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -38077,12 +38083,12 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>ALLD3.SA</t>
+          <t>JOPA4.SA</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Allied Tecnologia S.A.</t>
+          <t>JOSAPAR Joaquim Oliveira S.A. Participacoes</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
@@ -38092,16 +38098,16 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>95719928.2231722</v>
+        <v>36609422.50998402</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
@@ -38109,21 +38115,19 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.5967054981809672</v>
+        <v>0.5958543002410283</v>
       </c>
       <c r="K9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.31638625</v>
-      </c>
-      <c r="M9" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3091084</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>1.95</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>0.09002446</v>
+        <v>0.11179082</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -38132,12 +38136,12 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>JOPA4.SA</t>
+          <t>ENJU3.SA</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>JOSAPAR Joaquim Oliveira S.A. Participacoes</t>
+          <t>Enjoei.com.br Atividades de Internet S.A.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -38147,36 +38151,36 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>36609422.50998402</v>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>29552282.31995058</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.5958543002410283</v>
+        <v>0.5956568118421215</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>1</v>
+        <v>0.524</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.3091084</v>
+        <v>0.7389163</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>1.95</v>
+        <v>25.85</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>0.11179082</v>
+        <v>0.5409826</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -38185,12 +38189,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>ENJU3.SA</t>
+          <t>JOPA3.SA</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Enjoei.com.br Atividades de Internet S.A.</t>
+          <t>JOSAPAR Joaquim Oliveira S.A. Participacoes</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -38200,36 +38204,36 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>29552282.31995058</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>34778953.84455657</v>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.5956568118421215</v>
+        <v>0.5923365960998004</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.7389163</v>
+        <v>0.29365298</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>25.85</v>
+        <v>1.9</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>0.5409826</v>
+        <v>0.10620128</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -38238,12 +38242,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>JOPA3.SA</t>
+          <t>MDIA3.SA</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>JOSAPAR Joaquim Oliveira S.A. Participacoes</t>
+          <t>M. Dias Branco S.A. Industria e Comercio de Alimentos</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -38258,11 +38262,11 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>34778953.84455657</v>
+        <v>1146714624.544556</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -38270,19 +38274,19 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.5923365960998004</v>
+        <v>0.5862386096446587</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.29365298</v>
+        <v>0.7031003</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>1.9</v>
+        <v>2.0499999</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.10620128</v>
+        <v>0.5724966500000001</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -38291,12 +38295,12 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>MDIA3.SA</t>
+          <t>LPSB3.SA</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>M. Dias Branco S.A. Industria e Comercio de Alimentos</t>
+          <t>LPS Brasil - Consultoria de Imoveis S.A.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -38306,16 +38310,16 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>1146714624.544556</v>
+        <v>34037629.67188954</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -38323,19 +38327,19 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.5862386096446587</v>
+        <v>0.5768606702562663</v>
       </c>
       <c r="K13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.7031003</v>
+        <v>0.7321226</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>2.0499999</v>
+        <v>15.11</v>
       </c>
       <c r="N13" s="24" t="n">
-        <v>0.5724966500000001</v>
+        <v>0.8537754400000001</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -38344,12 +38348,12 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>LPSB3.SA</t>
+          <t>NGRD3.SA</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>LPS Brasil - Consultoria de Imoveis S.A.</t>
+          <t>Neogrid Participacoes S.A.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -38359,7 +38363,7 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -38368,27 +38372,29 @@
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>34037629.67188954</v>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>59864511.55574942</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.5768606702562663</v>
+        <v>0.5742882171665294</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.7321226</v>
-      </c>
-      <c r="M14" s="25" t="n">
-        <v>15.11</v>
+        <v>0.7064399</v>
+      </c>
+      <c r="M14" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.8537754400000001</v>
+        <v>1.1649072</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -38397,12 +38403,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>NGRD3.SA</t>
+          <t>MTRE3.SA</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Neogrid Participacoes S.A.</t>
+          <t>Mitre Realty Empreendimentos e Participacoes S.A.</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -38412,7 +38418,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -38421,29 +38427,27 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>59864511.55574942</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>69525834.50361443</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.5742882171665294</v>
+        <v>0.5720923309592543</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.5</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.7064399</v>
-      </c>
-      <c r="M15" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.35286835</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>14.72</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>1.1649072</v>
+        <v>0.32449642</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -38452,22 +38456,22 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>MTRE3.SA</t>
+          <t>ARA.MX</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Mitre Realty Empreendimentos e Participacoes S.A.</t>
+          <t>Consorcio ARA, S. A. B. de C. V.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -38476,7 +38480,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>69525834.50361443</v>
+        <v>330609920.7797604</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -38484,19 +38488,19 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.5720923309592543</v>
+        <v>0.5716130842084831</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.35286835</v>
+        <v>0.36474165</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>14.72</v>
+        <v>3.46</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.32449642</v>
+        <v>0.6642302</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -38505,51 +38509,51 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>ARA.MX</t>
+          <t>DOHL4.SA</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Consorcio ARA, S. A. B. de C. V.</t>
+          <t>Dohler S.A.</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>330609920.7797604</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>53827809.12946415</v>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.5716130842084831</v>
+        <v>0.5710518473946241</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.778</v>
+        <v>0.85</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.36474165</v>
+        <v>0.408007</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>3.46</v>
+        <v>0.9599999499999999</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.6642302</v>
+        <v>0.45073947</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -38558,7 +38562,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>DOHL4.SA</t>
+          <t>DOHL3.SA</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -38578,31 +38582,31 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>53827809.12946415</v>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>93224572.88957834</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.5710518473946241</v>
+        <v>0.5660682421020992</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.408007</v>
+        <v>0.70662874</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>0.9599999499999999</v>
+        <v>0.50999997</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.45073947</v>
+        <v>0.7806373</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -38611,31 +38615,31 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>DOHL3.SA</t>
+          <t>BYMA.BA</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Dohler S.A.</t>
+          <t>Bolsas y Mercados Argentinos S.A.</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>93224572.88957834</v>
+        <v>1400552783.034012</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -38643,19 +38647,19 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.5660682421020992</v>
+        <v>0.5635201777969934</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.8</v>
+        <v>0.765</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.70662874</v>
+        <v>3.0353515</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>0.50999997</v>
+        <v>9.370000000000001</v>
       </c>
       <c r="N19" s="24" t="n">
-        <v>0.7806373</v>
+        <v>7.011355</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -38664,17 +38668,17 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>BYMA.BA</t>
+          <t>BGIP3.SA</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Bolsas y Mercados Argentinos S.A.</t>
+          <t>Banco do Estado de Sergipe S.A.</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -38684,11 +38688,11 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>1400552783.034012</v>
+        <v>205704336.5073796</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -38696,19 +38700,19 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.5635201777969934</v>
+        <v>0.5629416095912552</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.765</v>
+        <v>1</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>3.0353515</v>
+        <v>1.0578787</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>9.370000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>7.011355</v>
+        <v>1.4172127</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -38717,22 +38721,22 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>BGIP3.SA</t>
+          <t>ANASAC.SN</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Banco do Estado de Sergipe S.A.</t>
+          <t>Agricola Nacional S.A.C. e I.</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -38741,7 +38745,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>205704336.5073796</v>
+        <v>59593464.32982922</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -38749,19 +38753,21 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.5629416095912552</v>
+        <v>0.5623952833200736</v>
       </c>
       <c r="K21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1.0578787</v>
-      </c>
-      <c r="M21" s="25" t="n">
-        <v>6.74</v>
+        <v>0.3956318221962061</v>
+      </c>
+      <c r="M21" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N21" s="24" t="n">
-        <v>1.4172127</v>
+        <v>0.2100532394615819</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -38770,22 +38776,22 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>ANASAC.SN</t>
+          <t>GMD.MX</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Agricola Nacional S.A.C. e I.</t>
+          <t>Grupo Mexicano de Desarrollo, S.A.B.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -38794,7 +38800,7 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>59593464.32982922</v>
+        <v>58530407.35249329</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -38802,13 +38808,13 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.5623952833200736</v>
+        <v>0.5566225999982054</v>
       </c>
       <c r="K22" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.3956318221962061</v>
+        <v>0.15660831</v>
       </c>
       <c r="M22" s="27" t="inlineStr">
         <is>
@@ -38816,7 +38822,7 @@
         </is>
       </c>
       <c r="N22" s="24" t="n">
-        <v>0.2100532394615819</v>
+        <v>0.15987411</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -38825,31 +38831,31 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>GMD.MX</t>
+          <t>EZTC3.SA</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Grupo Mexicano de Desarrollo, S.A.B.</t>
+          <t>EZTEC Empreendimentos e Participacoes S.A.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>58530407.35249329</v>
+        <v>692984451.5120659</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -38857,21 +38863,19 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.5566225999982054</v>
+        <v>0.5545637523198121</v>
       </c>
       <c r="K23" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.15660831</v>
-      </c>
-      <c r="M23" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.6891068</v>
+      </c>
+      <c r="M23" s="25" t="n">
+        <v>3.08</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0.15987411</v>
+        <v>2.5082033</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -38880,12 +38884,12 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>EZTC3.SA</t>
+          <t>SAPR3.SA</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>EZTEC Empreendimentos e Participacoes S.A.</t>
+          <t>Companhia de Saneamento do Parana - SANEPAR</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -38895,7 +38899,7 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -38904,7 +38908,7 @@
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>692984451.5120659</v>
+        <v>2233508789.351486</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -38912,19 +38916,19 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.5545637523198121</v>
+        <v>0.5442469337869011</v>
       </c>
       <c r="K24" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.6891068</v>
+        <v>0.19202437</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="N24" s="24" t="n">
-        <v>2.5082033</v>
+        <v>1.5407304</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -38933,12 +38937,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>SAPR3.SA</t>
+          <t>RSUL4.SA</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Companhia de Saneamento do Parana - SANEPAR</t>
+          <t>Metalurgica Riosulense S.A.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -38948,16 +38952,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>2233508789.351486</v>
+        <v>44661898.5066011</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -38965,19 +38969,19 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.5442469337869011</v>
+        <v>0.5425485918184764</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.19202437</v>
+        <v>0.8086806</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>2.4</v>
+        <v>8.59</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>1.5407304</v>
+        <v>0.55392486</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -38986,12 +38990,12 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>RSUL4.SA</t>
+          <t>SAPR4.SA</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Metalurgica Riosulense S.A.</t>
+          <t>Companhia de Saneamento do Parana - SANEPAR</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -39001,16 +39005,16 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>44661898.5066011</v>
+        <v>1986632126.145035</v>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
@@ -39018,19 +39022,19 @@
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.5425485918184764</v>
+        <v>0.5339559777662314</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.8086806</v>
+        <v>0.17079931</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>8.59</v>
+        <v>3.1</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>0.55392486</v>
+        <v>1.3704287</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -39039,12 +39043,12 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>SAPR4.SA</t>
+          <t>VINP</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Companhia de Saneamento do Parana - SANEPAR</t>
+          <t>Vinci Partners Investments Ltd.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -39054,7 +39058,7 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -39063,7 +39067,7 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>1986632126.145035</v>
+        <v>624343552</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -39071,19 +39075,19 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.5339559777662314</v>
+        <v>0.5229241070321009</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.17079931</v>
+        <v>1.5830834</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>3.1</v>
+        <v>6.94</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>1.3704287</v>
+        <v>0.5911029</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -39092,12 +39096,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>VINP</t>
+          <t>INTB3.SA</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Vinci Partners Investments Ltd.</t>
+          <t>Intelbras S.A. - Industria de Telecomunicacao Eletronica Bra</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -39107,7 +39111,7 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -39116,7 +39120,7 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>624343552</v>
+        <v>939542437.0234452</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -39124,19 +39128,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.5229241070321009</v>
+        <v>0.5223851566143971</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.5830834</v>
+        <v>1.4802337</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>6.94</v>
+        <v>10.0600004</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.5911029</v>
+        <v>1.0738517</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -1327,17 +1327,17 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>054800.KQ</t>
+          <t>1900.HK</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>IDIS Holdings Co., Ltd.</t>
+          <t>China ITS (Holdings) Co., Ltd.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -1347,31 +1347,33 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>85944326.25859833</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>36657145.75909615</v>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>1.17208086301225</v>
+        <v>1.182454295377496</v>
       </c>
       <c r="K9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.3329555299332747</v>
-      </c>
-      <c r="M9" s="25" t="n">
-        <v>2.21</v>
+        <v>0.13461347</v>
+      </c>
+      <c r="M9" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N9" s="24" t="n">
-        <v>0.13151133</v>
+        <v>0.30960968</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -1380,22 +1382,22 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>6155.T</t>
+          <t>054800.KQ</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Takamatsu Machinery Co., Ltd.</t>
+          <t>IDIS Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -1404,7 +1406,7 @@
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>36465264.94312406</v>
+        <v>85944326.25859833</v>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
@@ -1412,19 +1414,19 @@
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>1.168647419981598</v>
+        <v>1.17208086301225</v>
       </c>
       <c r="K10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.35892186</v>
+        <v>0.3329555299332747</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>0.46142256</v>
+        <v>0.13151133</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -1433,22 +1435,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>120240.KQ</t>
+          <t>6155.T</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Daejung Chemicals &amp; Metals Co.,Ltd.</t>
+          <t>Takamatsu Machinery Co., Ltd.</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -1457,7 +1459,7 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>68969379.53465939</v>
+        <v>36465264.94312406</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -1465,21 +1467,19 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>1.152290474548095</v>
+        <v>1.168647419981598</v>
       </c>
       <c r="K11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.5449940720767228</v>
-      </c>
-      <c r="M11" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.35892186</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <v>2.02</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>0.8796080168298662</v>
+        <v>0.46142256</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>035610.KQ</t>
+          <t>120240.KQ</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Solborn, Inc.</t>
+          <t>Daejung Chemicals &amp; Metals Co.,Ltd.</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>87016812.30957699</v>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>68969379.53465939</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>1.137221610175333</v>
+        <v>1.152290474548095</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.907</v>
+        <v>1</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.4404573070670534</v>
+        <v>0.5449940720767228</v>
       </c>
       <c r="M12" s="27" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="N12" s="24" t="n">
-        <v>1.0640486</v>
+        <v>0.8796080168298662</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1543,51 +1543,53 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>031510.KQ</t>
+          <t>3798.HK</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Austem Company Ltd.</t>
+          <t>Homeland Interactive Technology Ltd.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>18872311.0689466</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>193180522.7553062</v>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>1.128749512459602</v>
+        <v>1.146428117925815</v>
       </c>
       <c r="K13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.3574623360623071</v>
-      </c>
-      <c r="M13" s="25" t="n">
-        <v>2.0299999</v>
+        <v>0.63482887</v>
+      </c>
+      <c r="M13" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N13" s="24" t="n">
-        <v>0.20801528</v>
+        <v>1.2164296</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -1596,12 +1598,12 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>052330.KQ</t>
+          <t>035610.KQ</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Kortek Corporation</t>
+          <t>Solborn, Inc.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -1611,7 +1613,7 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -1620,27 +1622,29 @@
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>101813330.5148983</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>87016812.30957699</v>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>1.125043760681172</v>
+        <v>1.137221610175333</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.85</v>
+        <v>0.907</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.3869141557375681</v>
-      </c>
-      <c r="M14" s="25" t="n">
-        <v>2.79</v>
+        <v>0.4404573070670534</v>
+      </c>
+      <c r="M14" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.4606087</v>
+        <v>1.0640486</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1649,51 +1653,51 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>2348.HK</t>
+          <t>031510.KQ</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
+          <t>Austem Company Ltd.</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>189917124.4803295</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>18872311.0689466</v>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>1.09772165902702</v>
+        <v>1.128749512459602</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.37188843</v>
+        <v>0.3574623360623071</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>6.3</v>
+        <v>2.0299999</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>1.2983886</v>
+        <v>0.20801528</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1702,22 +1706,22 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>S23.SI</t>
+          <t>052330.KQ</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Singapura Finance Ltd</t>
+          <t>Kortek Corporation</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -1726,7 +1730,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>95521143.52214336</v>
+        <v>101813330.5148983</v>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
@@ -1734,19 +1738,19 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>1.077066150752263</v>
+        <v>1.125043760681172</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.46323967</v>
+        <v>0.3869141557375681</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>2.47</v>
+        <v>2.79</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>3.8912058</v>
+        <v>0.4606087</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1755,22 +1759,22 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>095660.KQ</t>
+          <t>2348.HK</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>NEOWIZ</t>
+          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -1779,7 +1783,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>227631179.1809044</v>
+        <v>189917124.4803295</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -1787,21 +1791,19 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>1.077025085586687</v>
+        <v>1.09772165902702</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.6557044396837195</v>
-      </c>
-      <c r="M17" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.37188843</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <v>6.3</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.7902293526088751</v>
+        <v>1.2983886</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -1810,22 +1812,22 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>051160.KQ</t>
+          <t>S23.SI</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>GaeaSoft Corp.</t>
+          <t>Singapura Finance Ltd</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -1834,29 +1836,27 @@
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>87192185.23034763</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>95521143.52214336</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>1.076677513729953</v>
+        <v>1.077066150752263</v>
       </c>
       <c r="K18" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.6916597246694085</v>
-      </c>
-      <c r="M18" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.46323967</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <v>2.47</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.22903164</v>
+        <v>3.8912058</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>014570.KQ</t>
+          <t>095660.KQ</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Korean Drug Co., Ltd.</t>
+          <t>NEOWIZ</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -1880,16 +1880,16 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>24818887.73322535</v>
+        <v>227631179.1809044</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -1897,19 +1897,21 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>1.076618108296869</v>
+        <v>1.077025085586687</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.4577384913211642</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>5.71</v>
+        <v>0.6557044396837195</v>
+      </c>
+      <c r="M19" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>0.5802912</v>
+        <v>0.7902293526088751</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -1918,51 +1920,53 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>1798.T</t>
+          <t>051160.KQ</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Moriya Corporation</t>
+          <t>GaeaSoft Corp.</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>72811760.47204256</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>87192185.23034763</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>1.070917345532181</v>
+        <v>1.076677513729953</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.62122</v>
-      </c>
-      <c r="M20" s="25" t="n">
-        <v>3.48</v>
+        <v>0.6916597246694085</v>
+      </c>
+      <c r="M20" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N20" s="24" t="n">
-        <v>0.24462086</v>
+        <v>0.22903164</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -1971,22 +1975,22 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>0114.HK</t>
+          <t>014570.KQ</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Herald Holdings Limited</t>
+          <t>Korean Drug Co., Ltd.</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -1995,27 +1999,27 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>50909684.39264202</v>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>24818887.73322535</v>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>1.069667882368217</v>
+        <v>1.076618108296869</v>
       </c>
       <c r="K21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.6560636</v>
+        <v>0.4577384913211642</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>9.379999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>0.49798346</v>
+        <v>0.5802912</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -2024,51 +2028,53 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>264450.KQ</t>
+          <t>2101.HK</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Ubiquoss Inc.</t>
+          <t>Fulu Holdings Limited</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>97170111.41296196</v>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>49478730.98710728</v>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>1.069418830089167</v>
+        <v>1.076342790435301</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.975</v>
+        <v>0.85</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.9925171574056828</v>
-      </c>
-      <c r="M22" s="25" t="n">
-        <v>4.9200002</v>
+        <v>0.26714593</v>
+      </c>
+      <c r="M22" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N22" s="24" t="n">
-        <v>1.2602726</v>
+        <v>1.3548405</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -2077,12 +2083,12 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>4301.T</t>
+          <t>1798.T</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Amuse Inc.</t>
+          <t>Moriya Corporation</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -2092,16 +2098,16 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>191774490.9876108</v>
+        <v>72811760.47204256</v>
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
@@ -2109,19 +2115,19 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>1.066874883462697</v>
+        <v>1.070917345532181</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.85901433</v>
+        <v>0.62122</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0.47582158</v>
+        <v>0.24462086</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -2130,51 +2136,51 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>4629.T</t>
+          <t>6820.HK</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Daishin Chemical Co.,Ltd.</t>
+          <t>FriendTimes Inc.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>68171702.99383163</v>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>94713120.1414652</v>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>1.065783945891929</v>
+        <v>1.070017765652008</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.6093777</v>
+        <v>0.49782798</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>2.4300002</v>
+        <v>5.63</v>
       </c>
       <c r="N24" s="24" t="n">
-        <v>0.28919291</v>
+        <v>0.6063374</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -2183,22 +2189,22 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>7871.T</t>
+          <t>0114.HK</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Fukuvi Chemical Industry Co.,Ltd.</t>
+          <t>Herald Holdings Limited</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -2207,27 +2213,27 @@
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>123512823.5460806</v>
-      </c>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>50909684.39264202</v>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>1.063903915619514</v>
+        <v>1.069667882368217</v>
       </c>
       <c r="K25" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.49369588</v>
+        <v>0.6560636</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>3.36</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>0.4746139</v>
+        <v>0.49798346</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -2236,51 +2242,51 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>6912.KL</t>
+          <t>264450.KQ</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Pasdec Holdings Bhd</t>
+          <t>Ubiquoss Inc.</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>29092297.90078092</v>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>97170111.41296196</v>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>1.04901245403616</v>
+        <v>1.069418830089167</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.28068504</v>
+        <v>0.9925171574056828</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>5.08</v>
+        <v>4.9200002</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>1.2228315</v>
+        <v>1.2602726</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -2289,51 +2295,51 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>053980.KQ</t>
+          <t>4301.T</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Osangjaiel Co., Ltd.</t>
+          <t>Amuse Inc.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>30341326.35495377</v>
-      </c>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>191774490.9876108</v>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>1.030492076157528</v>
+        <v>1.066874883462697</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.4894186186926682</v>
+        <v>0.85901433</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>6.1100002</v>
+        <v>3.55</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.35614914</v>
+        <v>0.47582158</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -2342,31 +2348,31 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>5MZ.SI</t>
+          <t>4629.T</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Kingsmen Creatives Ltd.</t>
+          <t>Daishin Chemical Co.,Ltd.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>83349515.04073143</v>
+        <v>68171702.99383163</v>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
@@ -2374,19 +2380,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>1.025807380872433</v>
+        <v>1.065783945891929</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.8656959</v>
+        <v>0.6093777</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>5.609999999999999</v>
+        <v>2.4300002</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.28319883</v>
+        <v>0.28919291</v>
       </c>
     </row>
   </sheetData>
@@ -7435,53 +7441,51 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>1900.HK</t>
+          <t>IRC.BK</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>China ITS (Holdings) Co., Ltd.</t>
+          <t>Inoue Rubber (Thailand) Public Company Limited</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H4" s="22" t="n">
-        <v>36657145.75909615</v>
-      </c>
-      <c r="I4" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>78821510.97271729</v>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J4" s="24" t="n">
-        <v>1.182454295377496</v>
+        <v>1.171785579179148</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="24" t="n">
-        <v>0.13461347</v>
-      </c>
-      <c r="M4" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.610335</v>
+      </c>
+      <c r="M4" s="25" t="n">
+        <v>4.21</v>
       </c>
       <c r="N4" s="24" t="n">
-        <v>0.30960968</v>
+        <v>0.5794926</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -7490,12 +7494,12 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>IRC.BK</t>
+          <t>TPP.BK</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Inoue Rubber (Thailand) Public Company Limited</t>
+          <t>Thai Packaging &amp; Printing Public Company Limited</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
@@ -7510,11 +7514,11 @@
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>78821510.97271729</v>
+        <v>14694714.95424652</v>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
@@ -7522,19 +7526,19 @@
         </is>
       </c>
       <c r="J5" s="24" t="n">
-        <v>1.171785579179148</v>
+        <v>1.164103836676694</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="L5" s="24" t="n">
-        <v>0.610335</v>
+        <v>0.5009125</v>
       </c>
       <c r="M5" s="25" t="n">
-        <v>4.21</v>
+        <v>8.33</v>
       </c>
       <c r="N5" s="24" t="n">
-        <v>0.5794926</v>
+        <v>1.6125863</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -7543,12 +7547,12 @@
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>TPP.BK</t>
+          <t>METCO.BK</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Thai Packaging &amp; Printing Public Company Limited</t>
+          <t>Muramoto Electron (Thailand) Public Company Limited</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
@@ -7558,16 +7562,16 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>14694714.95424652</v>
+        <v>189173887.7198486</v>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
@@ -7575,19 +7579,19 @@
         </is>
       </c>
       <c r="J6" s="24" t="n">
-        <v>1.164103836676694</v>
+        <v>1.095391292032167</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="L6" s="24" t="n">
-        <v>0.5009125</v>
+        <v>0.8462543</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>8.33</v>
+        <v>10.24</v>
       </c>
       <c r="N6" s="24" t="n">
-        <v>1.6125863</v>
+        <v>0.3770226</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -7596,53 +7600,51 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>3798.HK</t>
+          <t>BENGALT.BO</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Homeland Interactive Technology Ltd.</t>
+          <t>Bengal Tea &amp; Fabrics Limited</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>193180522.7553062</v>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>13105923.0400461</v>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J7" s="24" t="n">
-        <v>1.146428117925815</v>
+        <v>1.066842547335759</v>
       </c>
       <c r="K7" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="24" t="n">
-        <v>0.63482887</v>
-      </c>
-      <c r="M7" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.6409637</v>
+      </c>
+      <c r="M7" s="25" t="n">
+        <v>1.07</v>
       </c>
       <c r="N7" s="24" t="n">
-        <v>1.2164296</v>
+        <v>2.3847694</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -7651,12 +7653,12 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>METCO.BK</t>
+          <t>SIAM.BK</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Muramoto Electron (Thailand) Public Company Limited</t>
+          <t>Siam Steel International Public Company Limited</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
@@ -7666,36 +7668,38 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>189173887.7198486</v>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>16575814.47229004</v>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>1.095391292032167</v>
+        <v>1.063964737624092</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>0.8462543</v>
-      </c>
-      <c r="M8" s="25" t="n">
-        <v>10.24</v>
+        <v>0.21445222</v>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N8" s="24" t="n">
-        <v>0.3770226</v>
+        <v>0.42413014</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -7704,31 +7708,31 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>2101.HK</t>
+          <t>SPG.BK</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Fulu Holdings Limited</t>
+          <t>Siam Pan Group Public Company Limited</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>49478730.98710728</v>
+        <v>127855413.6385498</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
@@ -7736,21 +7740,19 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>1.076342790435301</v>
+        <v>1.05043788016529</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.26714593</v>
-      </c>
-      <c r="M9" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.71403486</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>7.27</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>1.3548405</v>
+        <v>1.9036341</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -7759,31 +7761,31 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>6820.HK</t>
+          <t>6912.KL</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>FriendTimes Inc.</t>
+          <t>Pasdec Holdings Bhd</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>94713120.1414652</v>
+        <v>29092297.90078092</v>
       </c>
       <c r="I10" s="26" t="inlineStr">
         <is>
@@ -7791,19 +7793,19 @@
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>1.070017765652008</v>
+        <v>1.04901245403616</v>
       </c>
       <c r="K10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.49782798</v>
+        <v>0.28068504</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>5.63</v>
+        <v>5.08</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>0.6063374</v>
+        <v>1.2228315</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -7812,22 +7814,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>BENGALT.BO</t>
+          <t>BUI.BK</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Bengal Tea &amp; Fabrics Limited</t>
+          <t>Bangkok Union Insurance Public Company Limited</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -7836,27 +7838,27 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>13105923.0400461</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>20846453.88253784</v>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>1.066842547335759</v>
+        <v>1.047527838830508</v>
       </c>
       <c r="K11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.6409637</v>
+        <v>0.53960043</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>1.07</v>
+        <v>1.83</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>2.3847694</v>
+        <v>0.48794216</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -7865,17 +7867,17 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>SIAM.BK</t>
+          <t>SHRIDINE.BO</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Siam Steel International Public Company Limited</t>
+          <t>Shri Dinesh Mills Limited</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -7889,29 +7891,27 @@
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>16575814.47229004</v>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>21685160.35478532</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>1.063964737624092</v>
+        <v>1.04658677837525</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.21445222</v>
-      </c>
-      <c r="M12" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.0360159</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <v>0.5599999999999999</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.42413014</v>
+        <v>2.9730365</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -7920,31 +7920,31 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>SPG.BK</t>
+          <t>002758.SZ</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Siam Pan Group Public Company Limited</t>
+          <t>ZJAMP Group Co., Ltd.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>127855413.6385498</v>
+        <v>687084527.9857178</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -7952,19 +7952,19 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>1.05043788016529</v>
+        <v>1.000196582679815</v>
       </c>
       <c r="K13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.71403486</v>
+        <v>0.90422845</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>7.27</v>
+        <v>3.58</v>
       </c>
       <c r="N13" s="24" t="n">
-        <v>1.9036341</v>
+        <v>0.093187146</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -7973,31 +7973,31 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>BUI.BK</t>
+          <t>200570.SZ</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Bangkok Union Insurance Public Company Limited</t>
+          <t>Changchai Company, Limited</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>20846453.88253784</v>
+        <v>190905360.9040813</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -8005,19 +8005,19 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>1.047527838830508</v>
+        <v>0.9971632762149122</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>1</v>
+        <v>0.965</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.53960043</v>
+        <v>0.36166108</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.48794216</v>
+        <v>0.5787663</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>SHRIDINE.BO</t>
+          <t>HMVL.NS</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Shri Dinesh Mills Limited</t>
+          <t>Hindustan Media Ventures Limited</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -8041,36 +8041,38 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>21685160.35478532</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>64503211.89800978</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>1.04658677837525</v>
+        <v>0.9958180552533994</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.8</v>
+        <v>0.855</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>1.0360159</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.38883346</v>
+      </c>
+      <c r="M15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N15" s="24" t="n">
-        <v>2.9730365</v>
+        <v>0.7992803000000001</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -8079,31 +8081,31 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>1281.HK</t>
+          <t>BEC.BK</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>LongiTech Smart Energy Holding Limited</t>
+          <t>BEC World Public Company Limited</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>17239267.37836957</v>
+        <v>117861490.2496338</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -8111,21 +8113,19 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>1.044435207391121</v>
+        <v>0.987347177946116</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.13935617</v>
-      </c>
-      <c r="M16" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.6432361</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <v>4.8499998</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>1.2005275</v>
+        <v>1.0562829</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -8134,17 +8134,17 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>9983.HK</t>
+          <t>MDX.BK</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Central China New Life Limited</t>
+          <t>MDX Public Company Limited</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8154,11 +8154,11 @@
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>49346205.81053686</v>
+        <v>50564280.4107666</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -8166,19 +8166,21 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>1.02348481150569</v>
+        <v>0.9583990102048631</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.8</v>
+        <v>0.675</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.17813413</v>
-      </c>
-      <c r="M17" s="25" t="n">
-        <v>35.529998</v>
+        <v>0.3252788</v>
+      </c>
+      <c r="M17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.14814928</v>
+        <v>4.510015</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -8187,51 +8189,51 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>002758.SZ</t>
+          <t>0149.KL</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>ZJAMP Group Co., Ltd.</t>
+          <t>FIBON</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>687084527.9857178</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>10229479.19960678</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>1.000196582679815</v>
+        <v>0.955960764980729</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>1</v>
+        <v>0.851</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.90422845</v>
+        <v>0.5829904</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.093187146</v>
+        <v>1.474617</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -8240,31 +8242,29 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>200570.SZ</t>
+          <t>5843.KL</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Changchai Company, Limited</t>
+          <t>Kumpulan Perangsang Selangor Bhd</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v/>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>190905360.9040813</v>
+        <v>71478428.8847394</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -8272,19 +8272,19 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.9971632762149122</v>
+        <v>0.9532334049037992</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.965</v>
+        <v>1</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.36166108</v>
+        <v>0.26587892</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>1.35</v>
+        <v>9.090000400000001</v>
       </c>
       <c r="N19" s="24" t="n">
-        <v>0.5787663</v>
+        <v>0.29897594</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -8293,31 +8293,31 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>HMVL.NS</t>
+          <t>INSURE.BK</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Hindustan Media Ventures Limited</t>
+          <t>Indara Insurance Public Company Limited</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>64503211.89800978</v>
+        <v>17132443.42803955</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -8325,21 +8325,19 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.9958180552533994</v>
+        <v>0.948074761144672</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.855</v>
+        <v>1</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.38883346</v>
-      </c>
-      <c r="M20" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.40026233</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>16.67</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>0.7992803000000001</v>
+        <v>0.094295114</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -8348,22 +8346,22 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>BEC.BK</t>
+          <t>RALS.JK</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>BEC World Public Company Limited</t>
+          <t>PT Ramayana Lestari Sentosa Tbk</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -8372,7 +8370,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>117861490.2496338</v>
+        <v>129506075.1105785</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -8380,19 +8378,19 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.987347177946116</v>
+        <v>0.9382281897735691</v>
       </c>
       <c r="K21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.6432361</v>
+        <v>0.6793851</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>4.8499998</v>
+        <v>13.59</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>1.0562829</v>
+        <v>1.0830034</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -8401,12 +8399,12 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>MDX.BK</t>
+          <t>CSC.BK</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>MDX Public Company Limited</t>
+          <t>Crown Seal Public Company Limited</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -8416,7 +8414,7 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -8425,7 +8423,7 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>50564280.4107666</v>
+        <v>74241692.440979</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -8433,21 +8431,19 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.9583990102048631</v>
+        <v>0.9227431789173527</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.675</v>
+        <v>1</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.3252788</v>
-      </c>
-      <c r="M22" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.56644934</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>5.11</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>4.510015</v>
+        <v>0.6689316</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -8456,51 +8452,51 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>0149.KL</t>
+          <t>HGS.NS</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>FIBON</t>
+          <t>Hinduja Global Solutions Limited</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>10229479.19960678</v>
-      </c>
-      <c r="I23" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>192958807.2054291</v>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.955960764980729</v>
+        <v>0.9195120747576538</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.851</v>
+        <v>0.75</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.5829904</v>
+        <v>0.22226703</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>1.474617</v>
+        <v>0.42924425</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -8509,31 +8505,31 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>3332.HK</t>
+          <t>5134.KL</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Nanjing Sinolife United Company Limited</t>
+          <t>Southern Acids M Bhd</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>18112824.91377163</v>
+        <v>104560759.758884</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -8541,21 +8537,19 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.952671284294316</v>
+        <v>0.9133086407760054</v>
       </c>
       <c r="K24" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.29117176</v>
-      </c>
-      <c r="M24" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.54025793</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <v>1.61</v>
       </c>
       <c r="N24" s="24" t="n">
-        <v>0.17043073</v>
+        <v>0.45006964</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -8564,12 +8558,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>INSURE.BK</t>
+          <t>TTT.BK</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Indara Insurance Public Company Limited</t>
+          <t>Toray Textiles (Thailand) Public Company Limited</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -8579,16 +8573,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>17132443.42803955</v>
+        <v>82578373.43493652</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -8596,19 +8590,19 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.948074761144672</v>
+        <v>0.9128266970532991</v>
       </c>
       <c r="K25" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.40026233</v>
+        <v>0.37471995</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>16.67</v>
+        <v>8.450000000000001</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>0.094295114</v>
+        <v>0.35801673</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -8617,51 +8611,51 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>RALS.JK</t>
+          <t>LEE.BK</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>PT Ramayana Lestari Sentosa Tbk</t>
+          <t>Lee Feed Mill Public Company Limited</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>129506075.1105785</v>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>66580666.41314697</v>
+      </c>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.9382281897735691</v>
+        <v>0.9060901045284493</v>
       </c>
       <c r="K26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.6793851</v>
+        <v>0.7892204</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>13.59</v>
+        <v>8.129999999999999</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>1.0830034</v>
+        <v>0.80654985</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -8670,31 +8664,31 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>CSC.BK</t>
+          <t>600335.SS</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Crown Seal Public Company Limited</t>
+          <t>Sinomach Automobile Co., Ltd.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>74241692.440979</v>
+        <v>1141068794.381958</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -8702,19 +8696,19 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.9227431789173527</v>
+        <v>0.9046637839430515</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.56644934</v>
+        <v>0.6641925</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>5.11</v>
+        <v>2.29</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.6689316</v>
+        <v>0.22615293</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -8723,51 +8717,51 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>HGS.NS</t>
+          <t>SAT.BK</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Hinduja Global Solutions Limited</t>
+          <t>Somboon Advance Technology Public Company Limited</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>192958807.2054291</v>
-      </c>
-      <c r="I28" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>209238814.4542236</v>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.9195120747576538</v>
+        <v>0.9008444539807795</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.22226703</v>
+        <v>0.80361134</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>1.25</v>
+        <v>10.13</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.42924425</v>
+        <v>1.008249</v>
       </c>
     </row>
   </sheetData>
@@ -8846,7 +8840,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9808,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -10626,16 +10620,16 @@
         <v>6</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -14842,7 +14836,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18383,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -21194,7 +21188,7 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -21569,7 +21563,7 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -22162,7 +22156,7 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -22270,7 +22264,7 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -22749,7 +22743,7 @@
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -22963,7 +22957,7 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -23232,7 +23226,7 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -26126,7 +26120,7 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F101" s="20" t="n">
@@ -26230,7 +26224,7 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -29403,7 +29397,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -30383,7 +30377,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -31851,12 +31845,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>080010.KQ</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>eSang Networks Co.,Ltd</t>
+          <t>MarketWise Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31866,7 +31860,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -31875,7 +31869,7 @@
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>44083144.95630217</v>
+        <v>52056132</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31883,21 +31877,21 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.8437656426119454</v>
+        <v>0.8419509166594421</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>0.4318499805098363</v>
-      </c>
-      <c r="M12" s="27" t="inlineStr">
+        <v>0.85</v>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
+      <c r="M12" s="25" t="n">
+        <v>6.21</v>
+      </c>
       <c r="N12" s="24" t="n">
-        <v>0.5690626668871859</v>
+        <v>0.16395529</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31906,12 +31900,12 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>MarketWise Inc. Class A Common Stock</t>
+          <t>China Automotive Systems, Inc.</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -31921,7 +31915,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -31930,7 +31924,7 @@
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>52056132</v>
+        <v>162921792</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -31938,21 +31932,21 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.8419509166594421</v>
+        <v>0.8070056963728398</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L13" s="27" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>0.36712217</v>
+      </c>
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="M13" s="25" t="n">
-        <v>6.21</v>
-      </c>
       <c r="N13" s="24" t="n">
-        <v>0.16395529</v>
+        <v>0.19514817</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -31961,31 +31955,31 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CF.TO</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>China Automotive Systems, Inc.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>162921792</v>
+        <v>1050265741.957283</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -31993,21 +31987,19 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.8070056963728398</v>
+        <v>0.8049400286116412</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.36712217</v>
-      </c>
-      <c r="M14" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.5474207</v>
+      </c>
+      <c r="M14" s="25" t="n">
+        <v>2.8199999</v>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.19514817</v>
+        <v>0.6597851</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -32016,17 +32008,17 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>CF.TO</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -32036,11 +32028,11 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>1050265741.957283</v>
+        <v>85665360</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -32048,19 +32040,21 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.8049400286116412</v>
+        <v>0.803723573147715</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>2.5474207</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>2.8199999</v>
+        <v>0.8451832500000001</v>
+      </c>
+      <c r="M15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.6597851</v>
+        <v>3.1397655</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32069,12 +32063,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Neuphoria Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32084,16 +32078,16 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>85665360</v>
+        <v>20375158</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -32101,13 +32095,13 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.803723573147715</v>
+        <v>0.7985383481971811</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.8451832500000001</v>
+        <v>0.688962</v>
       </c>
       <c r="M16" s="27" t="inlineStr">
         <is>
@@ -32115,7 +32109,7 @@
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>3.1397655</v>
+        <v>1.578253622747588</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32124,12 +32118,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>ACTG</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics Inc.</t>
+          <t>Acacia Research Corporation</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32139,38 +32133,36 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>20375158</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>443044096</v>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.7985383481971811</v>
+        <v>0.7978305871255087</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.8</v>
+        <v>0.995</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.688962</v>
-      </c>
-      <c r="M17" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8410523</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>1.578253622747588</v>
+        <v>1.5915426</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32179,12 +32171,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>ACTG</t>
+          <t>RV1.F</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Acacia Research Corporation</t>
+          <t>Raven Industries, Inc.</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32203,27 +32195,27 @@
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>443044096</v>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>2481246551.957886</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.7978305871255087</v>
+        <v>0.787461511324353</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.995</v>
+        <v>0.85</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.8410523</v>
+        <v>5.6012883</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>0</v>
+        <v>2.4400001</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>1.5915426</v>
+        <v>1.6451783</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32232,31 +32224,31 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>RV1.F</t>
+          <t>SPOT.V</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Raven Industries, Inc.</t>
+          <t>GoldSpot Discoveries Corp.</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>2481246551.957886</v>
+        <v>32853827.51483989</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -32264,19 +32256,21 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.787461511324353</v>
+        <v>0.7808553959703856</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.85</v>
+        <v>0.651</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>5.6012883</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>2.4400001</v>
+        <v>0.63352823</v>
+      </c>
+      <c r="M19" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>1.6451783</v>
+        <v>3.6421437</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -32285,31 +32279,31 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>SPOT.V</t>
+          <t>HERE</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>GoldSpot Discoveries Corp.</t>
+          <t>Quantasing Group Limited</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>32853827.51483989</v>
+        <v>103874616</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -32317,13 +32311,13 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.7808553959703856</v>
+        <v>0.7794728688851164</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.651</v>
+        <v>0.764</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.63352823</v>
+        <v>0.8565221</v>
       </c>
       <c r="M20" s="27" t="inlineStr">
         <is>
@@ -32331,7 +32325,7 @@
         </is>
       </c>
       <c r="N20" s="24" t="n">
-        <v>3.6421437</v>
+        <v>0.09556232000000001</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
@@ -32340,12 +32334,12 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>HERE</t>
+          <t>OPBK</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Quantasing Group Limited</t>
+          <t>OP Bancorp</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -32355,7 +32349,7 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -32364,7 +32358,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>103874616</v>
+        <v>230858224</v>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
@@ -32372,21 +32366,19 @@
         </is>
       </c>
       <c r="J21" s="24" t="n">
-        <v>0.7794728688851164</v>
+        <v>0.7794514697914465</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.764</v>
+        <v>1</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>0.8565221</v>
-      </c>
-      <c r="M21" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9669752</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <v>3.53787792282389</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>0.09556232000000001</v>
+        <v>2.3767962</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -32395,12 +32387,12 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>OPBK</t>
+          <t>NOAH</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>OP Bancorp</t>
+          <t>Noah Holdings Ltd</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -32415,11 +32407,11 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>230858224</v>
+        <v>578683776</v>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
@@ -32427,19 +32419,19 @@
         </is>
       </c>
       <c r="J22" s="24" t="n">
-        <v>0.7794514697914465</v>
+        <v>0.7774229415579383</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.9669752</v>
+        <v>0.41539234</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>3.53787792282389</v>
+        <v>6.92</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>2.3767962</v>
+        <v>0.22156554</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -32448,12 +32440,12 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>NOAH</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Noah Holdings Ltd</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -32463,16 +32455,16 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>578683776</v>
+        <v>52732928</v>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
@@ -32480,19 +32472,21 @@
         </is>
       </c>
       <c r="J23" s="24" t="n">
-        <v>0.7774229415579383</v>
+        <v>0.7772382281821867</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.9419999999999999</v>
+        <v>1</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.41539234</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>6.92</v>
+        <v>0.78786975</v>
+      </c>
+      <c r="M23" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0.22156554</v>
+        <v>2.7442198</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
@@ -32501,12 +32495,12 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>GDOT</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Green Dot Corporation</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -32516,16 +32510,16 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>52732928</v>
+        <v>759612416</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -32533,13 +32527,13 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7772382281821867</v>
+        <v>0.7635526072015121</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>1</v>
+        <v>0.761</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.78786975</v>
+        <v>0.80861384</v>
       </c>
       <c r="M24" s="27" t="inlineStr">
         <is>
@@ -32547,7 +32541,7 @@
         </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>2.7442198</v>
+        <v>0.33199</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -32556,12 +32550,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>GDOT</t>
+          <t>HOOK</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Green Dot Corporation</t>
+          <t>HOOKIPA Pharma Inc.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -32571,16 +32565,16 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>759612416</v>
+        <v>14232977</v>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
@@ -32588,13 +32582,13 @@
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7635526072015121</v>
+        <v>0.7538404842957074</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>0.80861384</v>
+        <v>0.4961991702691395</v>
       </c>
       <c r="M25" s="27" t="inlineStr">
         <is>
@@ -32602,7 +32596,7 @@
         </is>
       </c>
       <c r="N25" s="24" t="n">
-        <v>0.33199</v>
+        <v>0.9580625336564352</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -32611,12 +32605,12 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>7060.KL</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>New Hoong Fatt Holdings Bhd</t>
+          <t>Huize Holding Limited</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -32626,7 +32620,7 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -32635,7 +32629,7 @@
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>53759979.84742952</v>
+        <v>14855932</v>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
@@ -32643,19 +32637,23 @@
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.758330402567876</v>
+        <v>0.7488690475248976</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.36964437</v>
-      </c>
-      <c r="M26" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="N26" s="24" t="n">
-        <v>0.93600476</v>
+        <v>0.2310821</v>
+      </c>
+      <c r="M26" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N26" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -32664,12 +32662,12 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>HOOK</t>
+          <t>LX</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>HOOKIPA Pharma Inc.</t>
+          <t>Lexinfintech Holdings Ltd.</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -32679,16 +32677,16 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>14232977</v>
+        <v>145293824</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -32696,21 +32694,21 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7538404842957074</v>
+        <v>0.7445146863770131</v>
       </c>
       <c r="K27" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.4961991702691395</v>
-      </c>
-      <c r="M27" s="27" t="inlineStr">
+        <v>0.08405468000000001</v>
+      </c>
+      <c r="M27" s="25" t="n">
+        <v>19.590001</v>
+      </c>
+      <c r="N27" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
-      </c>
-      <c r="N27" s="24" t="n">
-        <v>0.9580625336564352</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -32719,12 +32717,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Huize Holding Limited</t>
+          <t>Grid Dynamics Holdings, Inc.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -32734,16 +32732,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>14855932</v>
+        <v>653477056</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -32751,23 +32749,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.7488690475248976</v>
+        <v>0.7419661743672551</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.9</v>
+        <v>0.667</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.2310821</v>
-      </c>
-      <c r="M28" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N28" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.2560425</v>
+      </c>
+      <c r="M28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>1.5463948</v>
       </c>
     </row>
   </sheetData>
@@ -36297,7 +36291,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
@@ -39710,7 +39704,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42141,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -45205,22 +45199,22 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>1846.HK</t>
+          <t>WINE.L</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>EuroEyes International Eye Clinic Limited</t>
+          <t>Naked Wines plc</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -45229,7 +45223,7 @@
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>95640645.29344843</v>
+        <v>58703095.59600163</v>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
@@ -45237,19 +45231,21 @@
         </is>
       </c>
       <c r="J24" s="24" t="n">
-        <v>0.7397455743549545</v>
+        <v>0.7243912803567023</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.6124050599999999</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>1.07</v>
+        <v>75.368904</v>
+      </c>
+      <c r="M24" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N24" s="24" t="n">
-        <v>0.8583</v>
+        <v>0.22054756</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
@@ -45258,12 +45254,12 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>WINE.L</t>
+          <t>SNX.L</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Naked Wines plc</t>
+          <t>Synectics plc</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -45273,38 +45269,36 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>58703095.59600163</v>
-      </c>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>43201700.30317998</v>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J25" s="24" t="n">
-        <v>0.7243912803567023</v>
+        <v>0.7092167337860986</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>75.368904</v>
-      </c>
-      <c r="M25" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>75.54671500000001</v>
+      </c>
+      <c r="M25" s="25" t="n">
+        <v>2.5</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>0.22054756</v>
+        <v>0.5890832499999999</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
@@ -45313,17 +45307,17 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>SNX.L</t>
+          <t>SFPI.PA</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Synectics plc</t>
+          <t>Groupe SFPI SA</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -45333,31 +45327,31 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>43201700.30317998</v>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>208542190.0267181</v>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J26" s="24" t="n">
-        <v>0.7092167337860986</v>
+        <v>0.7061878566393767</v>
       </c>
       <c r="K26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>75.54671500000001</v>
+        <v>0.65529925</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>0.5890832499999999</v>
+        <v>0.28911924</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
@@ -45366,31 +45360,31 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>SFPI.PA</t>
+          <t>ARC.L</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Groupe SFPI SA</t>
+          <t>Arcontech Group plc</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>208542190.0267181</v>
+        <v>14034865.80596995</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -45398,19 +45392,19 @@
         </is>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.7061878566393767</v>
+        <v>0.7055115790768243</v>
       </c>
       <c r="K27" s="24" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.65529925</v>
+        <v>1.150761848157846</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>3.81</v>
+        <v>5.1599998</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.28911924</v>
+        <v>3.4588351</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
@@ -45419,22 +45413,22 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>ARC.L</t>
+          <t>ALTRI.PA</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Arcontech Group plc</t>
+          <t>Trilogiq S.A.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -45443,7 +45437,7 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>14034865.80596995</v>
+        <v>20635514.17211151</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -45451,19 +45445,21 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.7055115790768243</v>
+        <v>0.7020798395964118</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.150761848157846</v>
-      </c>
-      <c r="M28" s="25" t="n">
-        <v>5.1599998</v>
+        <v>0.56063575</v>
+      </c>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N28" s="24" t="n">
-        <v>3.4588351</v>
+        <v>0.8523706</v>
       </c>
     </row>
   </sheetData>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -31795,12 +31795,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>SBCWW</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Sbc Medical Group Holdings Incorporated</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31810,7 +31810,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -31819,7 +31819,7 @@
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>12773946</v>
+        <v>31542409.9725</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31827,23 +31827,21 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.8427237197322167</v>
+        <v>0.8417304836155266</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.571</v>
+        <v>0.8</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.6015113</v>
+        <v>0.12247278</v>
       </c>
       <c r="M12" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N12" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N12" s="24" t="n">
+        <v>0.1781037290964673</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31852,31 +31850,31 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>SBCWW</t>
+          <t>DC-A.TO</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Sbc Medical Group Holdings Incorporated</t>
+          <t>Dundee Corporation</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>31542409.9725</v>
+        <v>334198944.4364262</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -31884,13 +31882,13 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.8417304836155266</v>
+        <v>0.8416725320266993</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.8</v>
+        <v>0.891</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.12247278</v>
+        <v>0.81739134</v>
       </c>
       <c r="M13" s="27" t="inlineStr">
         <is>
@@ -31898,7 +31896,7 @@
         </is>
       </c>
       <c r="N13" s="24" t="n">
-        <v>0.1781037290964673</v>
+        <v>46.262455</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -31907,31 +31905,31 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>DC-A.TO</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Dundee Corporation</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>334198944.4364262</v>
+        <v>46763160</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -31939,13 +31937,13 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.8416725320266993</v>
+        <v>0.8386666752381667</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.891</v>
+        <v>1</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.81739134</v>
+        <v>0.69867694</v>
       </c>
       <c r="M14" s="27" t="inlineStr">
         <is>
@@ -31953,7 +31951,7 @@
         </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>46.262455</v>
+        <v>2.4335532</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -31962,12 +31960,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -31977,7 +31975,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -31986,7 +31984,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>46763160</v>
+        <v>12773946</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -31994,21 +31992,23 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.8386666752381667</v>
+        <v>0.832868113719865</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.69867694</v>
+        <v>0.6015113</v>
       </c>
       <c r="M15" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N15" s="24" t="n">
-        <v>2.4335532</v>
+      <c r="N15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32214,10 +32214,10 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.8068228581375196</v>
+        <v>0.8035042382866744</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.828</v>
+        <v>0.803</v>
       </c>
       <c r="L19" s="24" t="n">
         <v>0.2269332554781938</v>
@@ -50742,10 +50742,10 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.7483747819327972</v>
+        <v>0.7397178222661022</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
@@ -63517,10 +63517,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.6994979809618332</v>
+        <v>0.6964958437044864</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>0.9437919</v>
@@ -63733,10 +63733,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.6496446992604653</v>
+        <v>0.6454348598041391</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.739</v>
+        <v>0.701</v>
       </c>
       <c r="L13" s="24" t="n">
         <v>0.33102494</v>
@@ -63945,10 +63945,10 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.6088780483119204</v>
+        <v>0.6047375032446598</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.588</v>
+        <v>0.55</v>
       </c>
       <c r="L17" s="24" t="n">
         <v>0.7176173</v>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -31722,12 +31722,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -31737,16 +31737,16 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>12457237</v>
+        <v>63345280</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -31754,23 +31754,19 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.8444224464948391</v>
+        <v>0.8425192587847309</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.571</v>
+        <v>0.8</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.58659774</v>
-      </c>
-      <c r="M11" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N11" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>0.031039892</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -31779,12 +31775,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>SBCWW</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Sbc Medical Group Holdings Incorporated</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31794,16 +31790,16 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>63345280</v>
+        <v>31542409.9725</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31811,19 +31807,21 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.8425192587847309</v>
+        <v>0.8415046914231734</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.8</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="M12" s="25" t="n">
-        <v>0</v>
+        <v>0.12441679</v>
+      </c>
+      <c r="M12" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.031039892</v>
+        <v>0.1781037290964673</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31832,31 +31830,31 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>SBCWW</t>
+          <t>DC-A.TO</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Sbc Medical Group Holdings Incorporated</t>
+          <t>Dundee Corporation</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>31542409.9725</v>
+        <v>338077473.7864094</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -31864,13 +31862,13 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.8415046914231734</v>
+        <v>0.8403952351617557</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.8</v>
+        <v>0.891</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.12441679</v>
+        <v>0.8268775</v>
       </c>
       <c r="M13" s="27" t="inlineStr">
         <is>
@@ -31878,7 +31876,7 @@
         </is>
       </c>
       <c r="N13" s="24" t="n">
-        <v>0.1781037290964673</v>
+        <v>46.79935</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -31887,31 +31885,31 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>DC-A.TO</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Dundee Corporation</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>338077473.7864094</v>
+        <v>48653588</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -31919,13 +31917,13 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.8403952351617557</v>
+        <v>0.8386666752381667</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.891</v>
+        <v>1</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.8268775</v>
+        <v>0.7269213</v>
       </c>
       <c r="M14" s="27" t="inlineStr">
         <is>
@@ -31933,7 +31931,7 @@
         </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>46.79935</v>
+        <v>2.5319312</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -31942,12 +31940,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -31957,7 +31955,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -31966,7 +31964,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>48653588</v>
+        <v>12457237</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -31974,21 +31972,23 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.8386666752381667</v>
+        <v>0.8345469739695329</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.7269213</v>
+        <v>0.58659774</v>
       </c>
       <c r="M15" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N15" s="24" t="n">
-        <v>2.5319312</v>
+      <c r="N15" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32107,12 +32107,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32122,16 +32122,16 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>318702240</v>
+        <v>85936024</v>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
@@ -32139,13 +32139,13 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.8062111750244484</v>
+        <v>0.8033481199327791</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.828</v>
+        <v>0.95</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.2320380985386871</v>
+        <v>0.84785366</v>
       </c>
       <c r="M18" s="27" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         </is>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.64597005</v>
+        <v>2.366666409627936</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32162,12 +32162,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>XNET</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Xunlei Ltd</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -32177,16 +32177,16 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>85936024</v>
+        <v>318702240</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.8033481199327791</v>
+        <v>0.802895071145605</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.95</v>
+        <v>0.803</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.84785366</v>
+        <v>0.2320380985386871</v>
       </c>
       <c r="M19" s="27" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>2.366666409627936</v>
+        <v>0.64597005</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -50718,10 +50718,10 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.7483747819327972</v>
+        <v>0.7397178222661022</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
@@ -63491,10 +63491,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.6994979809618332</v>
+        <v>0.6964958437044864</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>0.9437919</v>
@@ -63707,10 +63707,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.6496446992604653</v>
+        <v>0.6454348598041391</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.739</v>
+        <v>0.701</v>
       </c>
       <c r="L13" s="24" t="n">
         <v>0.33102494</v>
@@ -63919,10 +63919,10 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.6088780483119204</v>
+        <v>0.6047375032446598</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.588</v>
+        <v>0.55</v>
       </c>
       <c r="L17" s="24" t="n">
         <v>0.7176173</v>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -31722,12 +31722,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -31737,16 +31737,16 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>63345280</v>
+        <v>12457237</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -31754,19 +31754,23 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.8425192587847309</v>
+        <v>0.8444224464948391</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="M11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="24" t="n">
-        <v>0.031039892</v>
+        <v>0.58659774</v>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N11" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -31775,12 +31779,12 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>SBCWW</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Sbc Medical Group Holdings Incorporated</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -31790,16 +31794,16 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>31542409.9725</v>
+        <v>63345280</v>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
@@ -31807,21 +31811,19 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.8415046914231734</v>
+        <v>0.8425192587847309</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.8</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.12441679</v>
-      </c>
-      <c r="M12" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.1781037290964673</v>
+        <v>0.031039892</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -31830,31 +31832,31 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>DC-A.TO</t>
+          <t>SBCWW</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Dundee Corporation</t>
+          <t>Sbc Medical Group Holdings Incorporated</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>338077473.7864094</v>
+        <v>31542409.9725</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -31862,13 +31864,13 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.8403952351617557</v>
+        <v>0.8415046914231734</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.891</v>
+        <v>0.8</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>0.8268775</v>
+        <v>0.12441679</v>
       </c>
       <c r="M13" s="27" t="inlineStr">
         <is>
@@ -31876,7 +31878,7 @@
         </is>
       </c>
       <c r="N13" s="24" t="n">
-        <v>46.79935</v>
+        <v>0.1781037290964673</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -31885,31 +31887,31 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>DC-A.TO</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Dundee Corporation</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>48653588</v>
+        <v>338077473.7864094</v>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
@@ -31917,13 +31919,13 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.8386666752381667</v>
+        <v>0.8403952351617557</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>1</v>
+        <v>0.891</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.7269213</v>
+        <v>0.8268775</v>
       </c>
       <c r="M14" s="27" t="inlineStr">
         <is>
@@ -31931,7 +31933,7 @@
         </is>
       </c>
       <c r="N14" s="24" t="n">
-        <v>2.5319312</v>
+        <v>46.79935</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -31940,12 +31942,12 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -31955,7 +31957,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -31964,7 +31966,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>12457237</v>
+        <v>48653588</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -31972,23 +31974,21 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.8345469739695329</v>
+        <v>0.8386666752381667</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.58659774</v>
+        <v>0.7269213</v>
       </c>
       <c r="M15" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N15" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N15" s="24" t="n">
+        <v>2.5319312</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -32107,12 +32107,12 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>SSBI</t>
+          <t>XNET</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Summit State Bank</t>
+          <t>Xunlei Ltd</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -32122,16 +32122,16 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>85936024</v>
+        <v>318702240</v>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
@@ -32139,13 +32139,13 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.8033481199327791</v>
+        <v>0.8062111750244484</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.95</v>
+        <v>0.828</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.84785366</v>
+        <v>0.2320380985386871</v>
       </c>
       <c r="M18" s="27" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         </is>
       </c>
       <c r="N18" s="24" t="n">
-        <v>2.366666409627936</v>
+        <v>0.64597005</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
@@ -32162,12 +32162,12 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>XNET</t>
+          <t>SSBI</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Xunlei Ltd</t>
+          <t>Summit State Bank</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -32177,16 +32177,16 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>318702240</v>
+        <v>85936024</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.802895071145605</v>
+        <v>0.8033481199327791</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.803</v>
+        <v>0.95</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>0.2320380985386871</v>
+        <v>0.84785366</v>
       </c>
       <c r="M19" s="27" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="N19" s="24" t="n">
-        <v>0.64597005</v>
+        <v>2.366666409627936</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
@@ -50718,10 +50718,10 @@
         </is>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.7397178222661022</v>
+        <v>0.7483747819327972</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
@@ -63491,10 +63491,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.6964958437044864</v>
+        <v>0.6994979809618332</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="L9" s="24" t="n">
         <v>0.9437919</v>
@@ -63707,10 +63707,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.6454348598041391</v>
+        <v>0.6496446992604653</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.701</v>
+        <v>0.739</v>
       </c>
       <c r="L13" s="24" t="n">
         <v>0.33102494</v>
@@ -63919,10 +63919,10 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.6047375032446598</v>
+        <v>0.6088780483119204</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.55</v>
+        <v>0.588</v>
       </c>
       <c r="L17" s="24" t="n">
         <v>0.7176173</v>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -12220,12 +12220,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>ANSGR.IS</t>
+          <t>MERIT.IS</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Anadolu Anonim Turk Sigorta Sirketi</t>
+          <t>Merit Turizm Yatirim ve Isletme Anonim Sirketi</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -12235,16 +12235,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>1153570162.652592</v>
+        <v>117290370.1971518</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -12252,19 +12252,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.4875212062086694</v>
+        <v>0.4875787113980344</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.667</v>
+        <v>0.738</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.3284723</v>
+        <v>0.26461387</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>4.9000002</v>
+        <v>6.41</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>0.5073823</v>
+        <v>16.029314</v>
       </c>
     </row>
   </sheetData>
@@ -32007,12 +32007,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32022,7 +32022,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -32031,7 +32031,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>48653588</v>
+        <v>12457237</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -32039,21 +32039,23 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.8081594299047473</v>
+        <v>0.8164227183294704</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>1</v>
+        <v>0.571</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.7269213</v>
+        <v>0.58659774</v>
       </c>
       <c r="M16" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N16" s="24" t="n">
-        <v>2.5319312</v>
+      <c r="N16" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32062,12 +32064,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32077,7 +32079,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -32086,7 +32088,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>12457237</v>
+        <v>48653588</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -32094,23 +32096,21 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.8068747010339026</v>
+        <v>0.8081594299047473</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.58659774</v>
+        <v>0.7269213</v>
       </c>
       <c r="M17" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N17" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N17" s="24" t="n">
+        <v>2.5319312</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32151,10 +32151,10 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.802895071145605</v>
+        <v>0.8062111750244484</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.803</v>
+        <v>0.828</v>
       </c>
       <c r="L18" s="24" t="n">
         <v>0.2320380985386871</v>
@@ -50737,10 +50737,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.7397178222661022</v>
+        <v>0.7483747819327972</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="L9" s="27" t="inlineStr">
         <is>
@@ -63573,10 +63573,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.619711718787281</v>
+        <v>0.6223828899889503</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="L11" s="24" t="n">
         <v>0.9437919</v>
@@ -63789,10 +63789,10 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.5742798753931376</v>
+        <v>0.578025607501778</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.701</v>
+        <v>0.739</v>
       </c>
       <c r="L15" s="24" t="n">
         <v>0.33102494</v>
@@ -64058,10 +64058,10 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.5520472864940897</v>
+        <v>0.555827069716932</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.55</v>
+        <v>0.588</v>
       </c>
       <c r="L20" s="24" t="n">
         <v>0.7176173</v>

--- a/asymmetry_nms_book.xlsx
+++ b/asymmetry_nms_book.xlsx
@@ -12220,12 +12220,12 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>MERIT.IS</t>
+          <t>ANSGR.IS</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Merit Turizm Yatirim ve Isletme Anonim Sirketi</t>
+          <t>Anadolu Anonim Turk Sigorta Sirketi</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -12235,16 +12235,16 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>117290370.1971518</v>
+        <v>1153570162.652592</v>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
@@ -12252,19 +12252,19 @@
         </is>
       </c>
       <c r="J28" s="24" t="n">
-        <v>0.4875787113980344</v>
+        <v>0.4875212062086694</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.738</v>
+        <v>0.667</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.26461387</v>
+        <v>1.3284723</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>6.41</v>
+        <v>4.9000002</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>16.029314</v>
+        <v>0.5073823</v>
       </c>
     </row>
   </sheetData>
@@ -32007,12 +32007,12 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>SCYNEXIS, Inc.</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -32022,7 +32022,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -32031,7 +32031,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>12457237</v>
+        <v>48653588</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -32039,23 +32039,21 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.8164227183294704</v>
+        <v>0.8081594299047473</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.58659774</v>
+        <v>0.7269213</v>
       </c>
       <c r="M16" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N16" s="27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N16" s="24" t="n">
+        <v>2.5319312</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -32064,12 +32062,12 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>SCYNEXIS, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -32079,7 +32077,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -32088,7 +32086,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>48653588</v>
+        <v>12457237</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -32096,21 +32094,23 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.8081594299047473</v>
+        <v>0.8068747010339026</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>0.7269213</v>
+        <v>0.58659774</v>
       </c>
       <c r="M17" s="27" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N17" s="24" t="n">
-        <v>2.5319312</v>
+      <c r="N17" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -32151,10 +32151,10 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.8062111750244484</v>
+        <v>0.802895071145605</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.828</v>
+        <v>0.803</v>
       </c>
       <c r="L18" s="24" t="n">
         <v>0.2320380985386871</v>
@@ -50737,10 +50737,10 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.7483747819327972</v>
+        <v>0.7397178222661022</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="L9" s="27" t="inlineStr">
         <is>
@@ -63573,10 +63573,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.6223828899889503</v>
+        <v>0.619711718787281</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="L11" s="24" t="n">
         <v>0.9437919</v>
@@ -63789,10 +63789,10 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.578025607501778</v>
+        <v>0.5742798753931376</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.739</v>
+        <v>0.701</v>
       </c>
       <c r="L15" s="24" t="n">
         <v>0.33102494</v>
@@ -64058,10 +64058,10 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.555827069716932</v>
+        <v>0.5520472864940897</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.588</v>
+        <v>0.55</v>
       </c>
       <c r="L20" s="24" t="n">
         <v>0.7176173</v>
